--- a/shabbat-planner.xlsx
+++ b/shabbat-planner.xlsx
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1129,6 +1129,18 @@
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>שינית שם של קבוצה ב«קבוצות»? עדכן אותו גם ב«שיבוץ» (חיפוש והחלפה). עמודת «בדיקה» שם תדליק אזהרה כתומה על כל שורה עם שם קבוצה שאינו קיים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>לשמור עותק לכל שבת: קובץ ← שמירה בשם ← «שבת פרשת ___».</t>
         </is>
@@ -1533,7 +1545,7 @@
         </is>
       </c>
       <c r="D4" s="20">
-        <f>'הגדרות'!$B$14</f>
+        <f>'הגדרות'!$B$14&amp;""</f>
         <v/>
       </c>
       <c r="E4" s="20" t="n"/>
@@ -1620,11 +1632,11 @@
         </is>
       </c>
       <c r="D8" s="20">
-        <f>'הגדרות'!$B$17</f>
+        <f>'הגדרות'!$B$17&amp;""</f>
         <v/>
       </c>
       <c r="E8" s="20">
-        <f>'הגדרות'!$B$22</f>
+        <f>'הגדרות'!$B$22&amp;""</f>
         <v/>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -1648,7 +1660,7 @@
         </is>
       </c>
       <c r="D9" s="20">
-        <f>'הגדרות'!$B$15</f>
+        <f>'הגדרות'!$B$15&amp;""</f>
         <v/>
       </c>
       <c r="E9" s="20" t="n"/>
@@ -1665,7 +1677,7 @@
         </is>
       </c>
       <c r="D10" s="20">
-        <f>'הגדרות'!$B$16</f>
+        <f>'הגדרות'!$B$16&amp;""</f>
         <v/>
       </c>
       <c r="E10" s="20" t="n"/>
@@ -1704,11 +1716,11 @@
         </is>
       </c>
       <c r="D12" s="20">
-        <f>'הגדרות'!$B$18</f>
+        <f>'הגדרות'!$B$18&amp;""</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f>'הגדרות'!$B$23</f>
+        <f>'הגדרות'!$B$23&amp;""</f>
         <v/>
       </c>
       <c r="F12" s="21">
@@ -1728,7 +1740,7 @@
         </is>
       </c>
       <c r="D13" s="20">
-        <f>'הגדרות'!$B$19</f>
+        <f>'הגדרות'!$B$19&amp;""</f>
         <v/>
       </c>
       <c r="E13" s="20" t="n"/>
@@ -1793,7 +1805,7 @@
       </c>
       <c r="D16" s="20" t="n"/>
       <c r="E16" s="20">
-        <f>'הגדרות'!$B$24</f>
+        <f>'הגדרות'!$B$24&amp;""</f>
         <v/>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -8244,7 +8256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8253,6 +8265,7 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col hidden="1" width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -8293,6 +8306,11 @@
           <t>מפתח (אל תיגעו)</t>
         </is>
       </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>בדיקה</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="58" t="inlineStr">
@@ -8316,6 +8334,10 @@
         <f>IF($A3="","",$A3&amp;"|"&amp;COUNTIF($A$3:$A3,$A3))</f>
         <v/>
       </c>
+      <c r="G3" s="32">
+        <f>IF($A3="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A3)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="58" t="inlineStr">
@@ -8343,6 +8365,10 @@
         <f>IF($A4="","",$A4&amp;"|"&amp;COUNTIF($A$3:$A4,$A4))</f>
         <v/>
       </c>
+      <c r="G4" s="32">
+        <f>IF($A4="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A4)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="58" t="inlineStr">
@@ -8368,6 +8394,10 @@
       <c r="E5" s="62" t="n"/>
       <c r="F5" s="63">
         <f>IF($A5="","",$A5&amp;"|"&amp;COUNTIF($A$3:$A5,$A5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="32">
+        <f>IF($A5="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A5)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>
@@ -8393,6 +8423,10 @@
         <f>IF($A6="","",$A6&amp;"|"&amp;COUNTIF($A$3:$A6,$A6))</f>
         <v/>
       </c>
+      <c r="G6" s="32">
+        <f>IF($A6="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A6)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="58" t="inlineStr">
@@ -8420,6 +8454,10 @@
         <f>IF($A7="","",$A7&amp;"|"&amp;COUNTIF($A$3:$A7,$A7))</f>
         <v/>
       </c>
+      <c r="G7" s="32">
+        <f>IF($A7="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A7)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="58" t="inlineStr">
@@ -8447,6 +8485,10 @@
         <f>IF($A8="","",$A8&amp;"|"&amp;COUNTIF($A$3:$A8,$A8))</f>
         <v/>
       </c>
+      <c r="G8" s="32">
+        <f>IF($A8="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A8)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="58" t="inlineStr">
@@ -8474,6 +8516,10 @@
         <f>IF($A9="","",$A9&amp;"|"&amp;COUNTIF($A$3:$A9,$A9))</f>
         <v/>
       </c>
+      <c r="G9" s="32">
+        <f>IF($A9="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A9)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="58" t="inlineStr">
@@ -8501,6 +8547,10 @@
         <f>IF($A10="","",$A10&amp;"|"&amp;COUNTIF($A$3:$A10,$A10))</f>
         <v/>
       </c>
+      <c r="G10" s="32">
+        <f>IF($A10="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A10)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="58" t="inlineStr">
@@ -8528,6 +8578,10 @@
         <f>IF($A11="","",$A11&amp;"|"&amp;COUNTIF($A$3:$A11,$A11))</f>
         <v/>
       </c>
+      <c r="G11" s="32">
+        <f>IF($A11="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A11)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="58" t="inlineStr">
@@ -8553,6 +8607,10 @@
       <c r="E12" s="62" t="n"/>
       <c r="F12" s="63">
         <f>IF($A12="","",$A12&amp;"|"&amp;COUNTIF($A$3:$A12,$A12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="32">
+        <f>IF($A12="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A12)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>
@@ -8578,6 +8636,10 @@
         <f>IF($A13="","",$A13&amp;"|"&amp;COUNTIF($A$3:$A13,$A13))</f>
         <v/>
       </c>
+      <c r="G13" s="32">
+        <f>IF($A13="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A13)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="58" t="inlineStr">
@@ -8601,6 +8663,10 @@
         <f>IF($A14="","",$A14&amp;"|"&amp;COUNTIF($A$3:$A14,$A14))</f>
         <v/>
       </c>
+      <c r="G14" s="32">
+        <f>IF($A14="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A14)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="58" t="inlineStr">
@@ -8628,6 +8694,10 @@
         <f>IF($A15="","",$A15&amp;"|"&amp;COUNTIF($A$3:$A15,$A15))</f>
         <v/>
       </c>
+      <c r="G15" s="32">
+        <f>IF($A15="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A15)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="58" t="inlineStr">
@@ -8653,6 +8723,10 @@
       <c r="E16" s="62" t="n"/>
       <c r="F16" s="63">
         <f>IF($A16="","",$A16&amp;"|"&amp;COUNTIF($A$3:$A16,$A16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>IF($A16="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A16)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>
@@ -8678,6 +8752,10 @@
         <f>IF($A17="","",$A17&amp;"|"&amp;COUNTIF($A$3:$A17,$A17))</f>
         <v/>
       </c>
+      <c r="G17" s="32">
+        <f>IF($A17="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A17)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="58" t="inlineStr">
@@ -8703,6 +8781,10 @@
       <c r="E18" s="62" t="n"/>
       <c r="F18" s="63">
         <f>IF($A18="","",$A18&amp;"|"&amp;COUNTIF($A$3:$A18,$A18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="32">
+        <f>IF($A18="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A18)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>
@@ -8728,6 +8810,10 @@
         <f>IF($A19="","",$A19&amp;"|"&amp;COUNTIF($A$3:$A19,$A19))</f>
         <v/>
       </c>
+      <c r="G19" s="32">
+        <f>IF($A19="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A19)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="58" t="inlineStr">
@@ -8751,6 +8837,10 @@
         <f>IF($A20="","",$A20&amp;"|"&amp;COUNTIF($A$3:$A20,$A20))</f>
         <v/>
       </c>
+      <c r="G20" s="32">
+        <f>IF($A20="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A20)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="58" t="inlineStr">
@@ -8778,6 +8868,10 @@
         <f>IF($A21="","",$A21&amp;"|"&amp;COUNTIF($A$3:$A21,$A21))</f>
         <v/>
       </c>
+      <c r="G21" s="32">
+        <f>IF($A21="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A21)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="58" t="inlineStr">
@@ -8803,6 +8897,10 @@
       <c r="E22" s="62" t="n"/>
       <c r="F22" s="63">
         <f>IF($A22="","",$A22&amp;"|"&amp;COUNTIF($A$3:$A22,$A22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="32">
+        <f>IF($A22="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A22)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>
@@ -8828,6 +8926,10 @@
         <f>IF($A23="","",$A23&amp;"|"&amp;COUNTIF($A$3:$A23,$A23))</f>
         <v/>
       </c>
+      <c r="G23" s="32">
+        <f>IF($A23="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A23)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="58" t="inlineStr">
@@ -8851,6 +8953,10 @@
         <f>IF($A24="","",$A24&amp;"|"&amp;COUNTIF($A$3:$A24,$A24))</f>
         <v/>
       </c>
+      <c r="G24" s="32">
+        <f>IF($A24="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A24)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="58" t="inlineStr">
@@ -8874,6 +8980,10 @@
         <f>IF($A25="","",$A25&amp;"|"&amp;COUNTIF($A$3:$A25,$A25))</f>
         <v/>
       </c>
+      <c r="G25" s="32">
+        <f>IF($A25="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A25)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="58" t="inlineStr">
@@ -8897,6 +9007,10 @@
         <f>IF($A26="","",$A26&amp;"|"&amp;COUNTIF($A$3:$A26,$A26))</f>
         <v/>
       </c>
+      <c r="G26" s="32">
+        <f>IF($A26="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A26)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="58" t="inlineStr">
@@ -8920,6 +9034,10 @@
         <f>IF($A27="","",$A27&amp;"|"&amp;COUNTIF($A$3:$A27,$A27))</f>
         <v/>
       </c>
+      <c r="G27" s="32">
+        <f>IF($A27="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A27)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="58" t="inlineStr">
@@ -8943,6 +9061,10 @@
         <f>IF($A28="","",$A28&amp;"|"&amp;COUNTIF($A$3:$A28,$A28))</f>
         <v/>
       </c>
+      <c r="G28" s="32">
+        <f>IF($A28="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A28)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="58" t="inlineStr">
@@ -8970,6 +9092,10 @@
         <f>IF($A29="","",$A29&amp;"|"&amp;COUNTIF($A$3:$A29,$A29))</f>
         <v/>
       </c>
+      <c r="G29" s="32">
+        <f>IF($A29="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A29)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="58" t="inlineStr">
@@ -8995,6 +9121,10 @@
       <c r="E30" s="62" t="n"/>
       <c r="F30" s="63">
         <f>IF($A30="","",$A30&amp;"|"&amp;COUNTIF($A$3:$A30,$A30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="32">
+        <f>IF($A30="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A30)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>
@@ -9020,6 +9150,10 @@
         <f>IF($A31="","",$A31&amp;"|"&amp;COUNTIF($A$3:$A31,$A31))</f>
         <v/>
       </c>
+      <c r="G31" s="32">
+        <f>IF($A31="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A31)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="58" t="inlineStr">
@@ -9043,6 +9177,10 @@
         <f>IF($A32="","",$A32&amp;"|"&amp;COUNTIF($A$3:$A32,$A32))</f>
         <v/>
       </c>
+      <c r="G32" s="32">
+        <f>IF($A32="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A32)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="58" t="inlineStr">
@@ -9070,6 +9208,10 @@
         <f>IF($A33="","",$A33&amp;"|"&amp;COUNTIF($A$3:$A33,$A33))</f>
         <v/>
       </c>
+      <c r="G33" s="32">
+        <f>IF($A33="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A33)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="58" t="inlineStr">
@@ -9095,6 +9237,10 @@
       <c r="E34" s="62" t="n"/>
       <c r="F34" s="63">
         <f>IF($A34="","",$A34&amp;"|"&amp;COUNTIF($A$3:$A34,$A34))</f>
+        <v/>
+      </c>
+      <c r="G34" s="32">
+        <f>IF($A34="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A34)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>
@@ -9108,6 +9254,10 @@
         <f>IF($A35="","",$A35&amp;"|"&amp;COUNTIF($A$3:$A35,$A35))</f>
         <v/>
       </c>
+      <c r="G35" s="32">
+        <f>IF($A35="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A35)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="58" t="n"/>
@@ -9119,6 +9269,10 @@
         <f>IF($A36="","",$A36&amp;"|"&amp;COUNTIF($A$3:$A36,$A36))</f>
         <v/>
       </c>
+      <c r="G36" s="32">
+        <f>IF($A36="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A36)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="58" t="n"/>
@@ -9130,6 +9284,10 @@
         <f>IF($A37="","",$A37&amp;"|"&amp;COUNTIF($A$3:$A37,$A37))</f>
         <v/>
       </c>
+      <c r="G37" s="32">
+        <f>IF($A37="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A37)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="58" t="n"/>
@@ -9141,6 +9299,10 @@
         <f>IF($A38="","",$A38&amp;"|"&amp;COUNTIF($A$3:$A38,$A38))</f>
         <v/>
       </c>
+      <c r="G38" s="32">
+        <f>IF($A38="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A38)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="58" t="n"/>
@@ -9152,6 +9314,10 @@
         <f>IF($A39="","",$A39&amp;"|"&amp;COUNTIF($A$3:$A39,$A39))</f>
         <v/>
       </c>
+      <c r="G39" s="32">
+        <f>IF($A39="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A39)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="58" t="n"/>
@@ -9163,6 +9329,10 @@
         <f>IF($A40="","",$A40&amp;"|"&amp;COUNTIF($A$3:$A40,$A40))</f>
         <v/>
       </c>
+      <c r="G40" s="32">
+        <f>IF($A40="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A40)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="58" t="n"/>
@@ -9174,6 +9344,10 @@
         <f>IF($A41="","",$A41&amp;"|"&amp;COUNTIF($A$3:$A41,$A41))</f>
         <v/>
       </c>
+      <c r="G41" s="32">
+        <f>IF($A41="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A41)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="58" t="n"/>
@@ -9185,6 +9359,10 @@
         <f>IF($A42="","",$A42&amp;"|"&amp;COUNTIF($A$3:$A42,$A42))</f>
         <v/>
       </c>
+      <c r="G42" s="32">
+        <f>IF($A42="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A42)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="58" t="n"/>
@@ -9196,6 +9374,10 @@
         <f>IF($A43="","",$A43&amp;"|"&amp;COUNTIF($A$3:$A43,$A43))</f>
         <v/>
       </c>
+      <c r="G43" s="32">
+        <f>IF($A43="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A43)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="58" t="n"/>
@@ -9207,6 +9389,10 @@
         <f>IF($A44="","",$A44&amp;"|"&amp;COUNTIF($A$3:$A44,$A44))</f>
         <v/>
       </c>
+      <c r="G44" s="32">
+        <f>IF($A44="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A44)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="58" t="n"/>
@@ -9218,6 +9404,10 @@
         <f>IF($A45="","",$A45&amp;"|"&amp;COUNTIF($A$3:$A45,$A45))</f>
         <v/>
       </c>
+      <c r="G45" s="32">
+        <f>IF($A45="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A45)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="58" t="n"/>
@@ -9229,6 +9419,10 @@
         <f>IF($A46="","",$A46&amp;"|"&amp;COUNTIF($A$3:$A46,$A46))</f>
         <v/>
       </c>
+      <c r="G46" s="32">
+        <f>IF($A46="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A46)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="58" t="n"/>
@@ -9240,6 +9434,10 @@
         <f>IF($A47="","",$A47&amp;"|"&amp;COUNTIF($A$3:$A47,$A47))</f>
         <v/>
       </c>
+      <c r="G47" s="32">
+        <f>IF($A47="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A47)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="58" t="n"/>
@@ -9251,6 +9449,10 @@
         <f>IF($A48="","",$A48&amp;"|"&amp;COUNTIF($A$3:$A48,$A48))</f>
         <v/>
       </c>
+      <c r="G48" s="32">
+        <f>IF($A48="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A48)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="58" t="n"/>
@@ -9262,6 +9464,10 @@
         <f>IF($A49="","",$A49&amp;"|"&amp;COUNTIF($A$3:$A49,$A49))</f>
         <v/>
       </c>
+      <c r="G49" s="32">
+        <f>IF($A49="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A49)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="58" t="n"/>
@@ -9273,6 +9479,10 @@
         <f>IF($A50="","",$A50&amp;"|"&amp;COUNTIF($A$3:$A50,$A50))</f>
         <v/>
       </c>
+      <c r="G50" s="32">
+        <f>IF($A50="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A50)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="58" t="n"/>
@@ -9284,6 +9494,10 @@
         <f>IF($A51="","",$A51&amp;"|"&amp;COUNTIF($A$3:$A51,$A51))</f>
         <v/>
       </c>
+      <c r="G51" s="32">
+        <f>IF($A51="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A51)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="58" t="n"/>
@@ -9295,6 +9509,10 @@
         <f>IF($A52="","",$A52&amp;"|"&amp;COUNTIF($A$3:$A52,$A52))</f>
         <v/>
       </c>
+      <c r="G52" s="32">
+        <f>IF($A52="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A52)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="58" t="n"/>
@@ -9306,6 +9524,10 @@
         <f>IF($A53="","",$A53&amp;"|"&amp;COUNTIF($A$3:$A53,$A53))</f>
         <v/>
       </c>
+      <c r="G53" s="32">
+        <f>IF($A53="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A53)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="58" t="n"/>
@@ -9317,6 +9539,10 @@
         <f>IF($A54="","",$A54&amp;"|"&amp;COUNTIF($A$3:$A54,$A54))</f>
         <v/>
       </c>
+      <c r="G54" s="32">
+        <f>IF($A54="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A54)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="58" t="n"/>
@@ -9328,6 +9554,10 @@
         <f>IF($A55="","",$A55&amp;"|"&amp;COUNTIF($A$3:$A55,$A55))</f>
         <v/>
       </c>
+      <c r="G55" s="32">
+        <f>IF($A55="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A55)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="58" t="n"/>
@@ -9339,6 +9569,10 @@
         <f>IF($A56="","",$A56&amp;"|"&amp;COUNTIF($A$3:$A56,$A56))</f>
         <v/>
       </c>
+      <c r="G56" s="32">
+        <f>IF($A56="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A56)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="58" t="n"/>
@@ -9350,6 +9584,10 @@
         <f>IF($A57="","",$A57&amp;"|"&amp;COUNTIF($A$3:$A57,$A57))</f>
         <v/>
       </c>
+      <c r="G57" s="32">
+        <f>IF($A57="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A57)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="58" t="n"/>
@@ -9361,6 +9599,10 @@
         <f>IF($A58="","",$A58&amp;"|"&amp;COUNTIF($A$3:$A58,$A58))</f>
         <v/>
       </c>
+      <c r="G58" s="32">
+        <f>IF($A58="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A58)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="58" t="n"/>
@@ -9372,6 +9614,10 @@
         <f>IF($A59="","",$A59&amp;"|"&amp;COUNTIF($A$3:$A59,$A59))</f>
         <v/>
       </c>
+      <c r="G59" s="32">
+        <f>IF($A59="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A59)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="58" t="n"/>
@@ -9383,6 +9629,10 @@
         <f>IF($A60="","",$A60&amp;"|"&amp;COUNTIF($A$3:$A60,$A60))</f>
         <v/>
       </c>
+      <c r="G60" s="32">
+        <f>IF($A60="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A60)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="58" t="n"/>
@@ -9394,6 +9644,10 @@
         <f>IF($A61="","",$A61&amp;"|"&amp;COUNTIF($A$3:$A61,$A61))</f>
         <v/>
       </c>
+      <c r="G61" s="32">
+        <f>IF($A61="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A61)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="58" t="n"/>
@@ -9405,6 +9659,10 @@
         <f>IF($A62="","",$A62&amp;"|"&amp;COUNTIF($A$3:$A62,$A62))</f>
         <v/>
       </c>
+      <c r="G62" s="32">
+        <f>IF($A62="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A62)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="58" t="n"/>
@@ -9416,6 +9674,10 @@
         <f>IF($A63="","",$A63&amp;"|"&amp;COUNTIF($A$3:$A63,$A63))</f>
         <v/>
       </c>
+      <c r="G63" s="32">
+        <f>IF($A63="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A63)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="58" t="n"/>
@@ -9427,6 +9689,10 @@
         <f>IF($A64="","",$A64&amp;"|"&amp;COUNTIF($A$3:$A64,$A64))</f>
         <v/>
       </c>
+      <c r="G64" s="32">
+        <f>IF($A64="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A64)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="58" t="n"/>
@@ -9438,6 +9704,10 @@
         <f>IF($A65="","",$A65&amp;"|"&amp;COUNTIF($A$3:$A65,$A65))</f>
         <v/>
       </c>
+      <c r="G65" s="32">
+        <f>IF($A65="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A65)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="58" t="n"/>
@@ -9449,6 +9719,10 @@
         <f>IF($A66="","",$A66&amp;"|"&amp;COUNTIF($A$3:$A66,$A66))</f>
         <v/>
       </c>
+      <c r="G66" s="32">
+        <f>IF($A66="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A66)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="58" t="n"/>
@@ -9460,6 +9734,10 @@
         <f>IF($A67="","",$A67&amp;"|"&amp;COUNTIF($A$3:$A67,$A67))</f>
         <v/>
       </c>
+      <c r="G67" s="32">
+        <f>IF($A67="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A67)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="58" t="n"/>
@@ -9471,6 +9749,10 @@
         <f>IF($A68="","",$A68&amp;"|"&amp;COUNTIF($A$3:$A68,$A68))</f>
         <v/>
       </c>
+      <c r="G68" s="32">
+        <f>IF($A68="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A68)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="58" t="n"/>
@@ -9482,6 +9764,10 @@
         <f>IF($A69="","",$A69&amp;"|"&amp;COUNTIF($A$3:$A69,$A69))</f>
         <v/>
       </c>
+      <c r="G69" s="32">
+        <f>IF($A69="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A69)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="58" t="n"/>
@@ -9493,6 +9779,10 @@
         <f>IF($A70="","",$A70&amp;"|"&amp;COUNTIF($A$3:$A70,$A70))</f>
         <v/>
       </c>
+      <c r="G70" s="32">
+        <f>IF($A70="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A70)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="58" t="n"/>
@@ -9504,6 +9794,10 @@
         <f>IF($A71="","",$A71&amp;"|"&amp;COUNTIF($A$3:$A71,$A71))</f>
         <v/>
       </c>
+      <c r="G71" s="32">
+        <f>IF($A71="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A71)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="58" t="n"/>
@@ -9515,6 +9809,10 @@
         <f>IF($A72="","",$A72&amp;"|"&amp;COUNTIF($A$3:$A72,$A72))</f>
         <v/>
       </c>
+      <c r="G72" s="32">
+        <f>IF($A72="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A72)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="58" t="n"/>
@@ -9526,6 +9824,10 @@
         <f>IF($A73="","",$A73&amp;"|"&amp;COUNTIF($A$3:$A73,$A73))</f>
         <v/>
       </c>
+      <c r="G73" s="32">
+        <f>IF($A73="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A73)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="58" t="n"/>
@@ -9537,6 +9839,10 @@
         <f>IF($A74="","",$A74&amp;"|"&amp;COUNTIF($A$3:$A74,$A74))</f>
         <v/>
       </c>
+      <c r="G74" s="32">
+        <f>IF($A74="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A74)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="58" t="n"/>
@@ -9548,6 +9854,10 @@
         <f>IF($A75="","",$A75&amp;"|"&amp;COUNTIF($A$3:$A75,$A75))</f>
         <v/>
       </c>
+      <c r="G75" s="32">
+        <f>IF($A75="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A75)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="58" t="n"/>
@@ -9559,6 +9869,10 @@
         <f>IF($A76="","",$A76&amp;"|"&amp;COUNTIF($A$3:$A76,$A76))</f>
         <v/>
       </c>
+      <c r="G76" s="32">
+        <f>IF($A76="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A76)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="58" t="n"/>
@@ -9570,6 +9884,10 @@
         <f>IF($A77="","",$A77&amp;"|"&amp;COUNTIF($A$3:$A77,$A77))</f>
         <v/>
       </c>
+      <c r="G77" s="32">
+        <f>IF($A77="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A77)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="58" t="n"/>
@@ -9581,6 +9899,10 @@
         <f>IF($A78="","",$A78&amp;"|"&amp;COUNTIF($A$3:$A78,$A78))</f>
         <v/>
       </c>
+      <c r="G78" s="32">
+        <f>IF($A78="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A78)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="58" t="n"/>
@@ -9592,6 +9914,10 @@
         <f>IF($A79="","",$A79&amp;"|"&amp;COUNTIF($A$3:$A79,$A79))</f>
         <v/>
       </c>
+      <c r="G79" s="32">
+        <f>IF($A79="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A79)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="58" t="n"/>
@@ -9603,6 +9929,10 @@
         <f>IF($A80="","",$A80&amp;"|"&amp;COUNTIF($A$3:$A80,$A80))</f>
         <v/>
       </c>
+      <c r="G80" s="32">
+        <f>IF($A80="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A80)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="58" t="n"/>
@@ -9614,6 +9944,10 @@
         <f>IF($A81="","",$A81&amp;"|"&amp;COUNTIF($A$3:$A81,$A81))</f>
         <v/>
       </c>
+      <c r="G81" s="32">
+        <f>IF($A81="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A81)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="58" t="n"/>
@@ -9625,6 +9959,10 @@
         <f>IF($A82="","",$A82&amp;"|"&amp;COUNTIF($A$3:$A82,$A82))</f>
         <v/>
       </c>
+      <c r="G82" s="32">
+        <f>IF($A82="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A82)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="58" t="n"/>
@@ -9636,6 +9974,10 @@
         <f>IF($A83="","",$A83&amp;"|"&amp;COUNTIF($A$3:$A83,$A83))</f>
         <v/>
       </c>
+      <c r="G83" s="32">
+        <f>IF($A83="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A83)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="58" t="n"/>
@@ -9647,6 +9989,10 @@
         <f>IF($A84="","",$A84&amp;"|"&amp;COUNTIF($A$3:$A84,$A84))</f>
         <v/>
       </c>
+      <c r="G84" s="32">
+        <f>IF($A84="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A84)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="58" t="n"/>
@@ -9658,6 +10004,10 @@
         <f>IF($A85="","",$A85&amp;"|"&amp;COUNTIF($A$3:$A85,$A85))</f>
         <v/>
       </c>
+      <c r="G85" s="32">
+        <f>IF($A85="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A85)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="58" t="n"/>
@@ -9669,6 +10019,10 @@
         <f>IF($A86="","",$A86&amp;"|"&amp;COUNTIF($A$3:$A86,$A86))</f>
         <v/>
       </c>
+      <c r="G86" s="32">
+        <f>IF($A86="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A86)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="58" t="n"/>
@@ -9680,6 +10034,10 @@
         <f>IF($A87="","",$A87&amp;"|"&amp;COUNTIF($A$3:$A87,$A87))</f>
         <v/>
       </c>
+      <c r="G87" s="32">
+        <f>IF($A87="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A87)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="58" t="n"/>
@@ -9691,6 +10049,10 @@
         <f>IF($A88="","",$A88&amp;"|"&amp;COUNTIF($A$3:$A88,$A88))</f>
         <v/>
       </c>
+      <c r="G88" s="32">
+        <f>IF($A88="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A88)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="58" t="n"/>
@@ -9702,6 +10064,10 @@
         <f>IF($A89="","",$A89&amp;"|"&amp;COUNTIF($A$3:$A89,$A89))</f>
         <v/>
       </c>
+      <c r="G89" s="32">
+        <f>IF($A89="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A89)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="58" t="n"/>
@@ -9713,6 +10079,10 @@
         <f>IF($A90="","",$A90&amp;"|"&amp;COUNTIF($A$3:$A90,$A90))</f>
         <v/>
       </c>
+      <c r="G90" s="32">
+        <f>IF($A90="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A90)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="58" t="n"/>
@@ -9724,6 +10094,10 @@
         <f>IF($A91="","",$A91&amp;"|"&amp;COUNTIF($A$3:$A91,$A91))</f>
         <v/>
       </c>
+      <c r="G91" s="32">
+        <f>IF($A91="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A91)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="58" t="n"/>
@@ -9735,6 +10109,10 @@
         <f>IF($A92="","",$A92&amp;"|"&amp;COUNTIF($A$3:$A92,$A92))</f>
         <v/>
       </c>
+      <c r="G92" s="32">
+        <f>IF($A92="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A92)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="58" t="n"/>
@@ -9746,6 +10124,10 @@
         <f>IF($A93="","",$A93&amp;"|"&amp;COUNTIF($A$3:$A93,$A93))</f>
         <v/>
       </c>
+      <c r="G93" s="32">
+        <f>IF($A93="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A93)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="58" t="n"/>
@@ -9757,6 +10139,10 @@
         <f>IF($A94="","",$A94&amp;"|"&amp;COUNTIF($A$3:$A94,$A94))</f>
         <v/>
       </c>
+      <c r="G94" s="32">
+        <f>IF($A94="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A94)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="58" t="n"/>
@@ -9768,6 +10154,10 @@
         <f>IF($A95="","",$A95&amp;"|"&amp;COUNTIF($A$3:$A95,$A95))</f>
         <v/>
       </c>
+      <c r="G95" s="32">
+        <f>IF($A95="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A95)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="58" t="n"/>
@@ -9779,6 +10169,10 @@
         <f>IF($A96="","",$A96&amp;"|"&amp;COUNTIF($A$3:$A96,$A96))</f>
         <v/>
       </c>
+      <c r="G96" s="32">
+        <f>IF($A96="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A96)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="58" t="n"/>
@@ -9790,6 +10184,10 @@
         <f>IF($A97="","",$A97&amp;"|"&amp;COUNTIF($A$3:$A97,$A97))</f>
         <v/>
       </c>
+      <c r="G97" s="32">
+        <f>IF($A97="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A97)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="58" t="n"/>
@@ -9801,6 +10199,10 @@
         <f>IF($A98="","",$A98&amp;"|"&amp;COUNTIF($A$3:$A98,$A98))</f>
         <v/>
       </c>
+      <c r="G98" s="32">
+        <f>IF($A98="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A98)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="58" t="n"/>
@@ -9812,6 +10214,10 @@
         <f>IF($A99="","",$A99&amp;"|"&amp;COUNTIF($A$3:$A99,$A99))</f>
         <v/>
       </c>
+      <c r="G99" s="32">
+        <f>IF($A99="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A99)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="58" t="n"/>
@@ -9823,6 +10229,10 @@
         <f>IF($A100="","",$A100&amp;"|"&amp;COUNTIF($A$3:$A100,$A100))</f>
         <v/>
       </c>
+      <c r="G100" s="32">
+        <f>IF($A100="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A100)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="58" t="n"/>
@@ -9834,6 +10244,10 @@
         <f>IF($A101="","",$A101&amp;"|"&amp;COUNTIF($A$3:$A101,$A101))</f>
         <v/>
       </c>
+      <c r="G101" s="32">
+        <f>IF($A101="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A101)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="58" t="n"/>
@@ -9845,6 +10259,10 @@
         <f>IF($A102="","",$A102&amp;"|"&amp;COUNTIF($A$3:$A102,$A102))</f>
         <v/>
       </c>
+      <c r="G102" s="32">
+        <f>IF($A102="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A102)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="58" t="n"/>
@@ -9856,6 +10274,10 @@
         <f>IF($A103="","",$A103&amp;"|"&amp;COUNTIF($A$3:$A103,$A103))</f>
         <v/>
       </c>
+      <c r="G103" s="32">
+        <f>IF($A103="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A103)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="58" t="n"/>
@@ -9867,6 +10289,10 @@
         <f>IF($A104="","",$A104&amp;"|"&amp;COUNTIF($A$3:$A104,$A104))</f>
         <v/>
       </c>
+      <c r="G104" s="32">
+        <f>IF($A104="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A104)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="58" t="n"/>
@@ -9878,6 +10304,10 @@
         <f>IF($A105="","",$A105&amp;"|"&amp;COUNTIF($A$3:$A105,$A105))</f>
         <v/>
       </c>
+      <c r="G105" s="32">
+        <f>IF($A105="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A105)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="58" t="n"/>
@@ -9889,6 +10319,10 @@
         <f>IF($A106="","",$A106&amp;"|"&amp;COUNTIF($A$3:$A106,$A106))</f>
         <v/>
       </c>
+      <c r="G106" s="32">
+        <f>IF($A106="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A106)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="58" t="n"/>
@@ -9900,6 +10334,10 @@
         <f>IF($A107="","",$A107&amp;"|"&amp;COUNTIF($A$3:$A107,$A107))</f>
         <v/>
       </c>
+      <c r="G107" s="32">
+        <f>IF($A107="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A107)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="58" t="n"/>
@@ -9911,6 +10349,10 @@
         <f>IF($A108="","",$A108&amp;"|"&amp;COUNTIF($A$3:$A108,$A108))</f>
         <v/>
       </c>
+      <c r="G108" s="32">
+        <f>IF($A108="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A108)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="58" t="n"/>
@@ -9922,6 +10364,10 @@
         <f>IF($A109="","",$A109&amp;"|"&amp;COUNTIF($A$3:$A109,$A109))</f>
         <v/>
       </c>
+      <c r="G109" s="32">
+        <f>IF($A109="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A109)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="58" t="n"/>
@@ -9933,6 +10379,10 @@
         <f>IF($A110="","",$A110&amp;"|"&amp;COUNTIF($A$3:$A110,$A110))</f>
         <v/>
       </c>
+      <c r="G110" s="32">
+        <f>IF($A110="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A110)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="58" t="n"/>
@@ -9944,6 +10394,10 @@
         <f>IF($A111="","",$A111&amp;"|"&amp;COUNTIF($A$3:$A111,$A111))</f>
         <v/>
       </c>
+      <c r="G111" s="32">
+        <f>IF($A111="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A111)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="58" t="n"/>
@@ -9955,6 +10409,10 @@
         <f>IF($A112="","",$A112&amp;"|"&amp;COUNTIF($A$3:$A112,$A112))</f>
         <v/>
       </c>
+      <c r="G112" s="32">
+        <f>IF($A112="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A112)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="58" t="n"/>
@@ -9966,6 +10424,10 @@
         <f>IF($A113="","",$A113&amp;"|"&amp;COUNTIF($A$3:$A113,$A113))</f>
         <v/>
       </c>
+      <c r="G113" s="32">
+        <f>IF($A113="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A113)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="58" t="n"/>
@@ -9977,6 +10439,10 @@
         <f>IF($A114="","",$A114&amp;"|"&amp;COUNTIF($A$3:$A114,$A114))</f>
         <v/>
       </c>
+      <c r="G114" s="32">
+        <f>IF($A114="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A114)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="58" t="n"/>
@@ -9988,6 +10454,10 @@
         <f>IF($A115="","",$A115&amp;"|"&amp;COUNTIF($A$3:$A115,$A115))</f>
         <v/>
       </c>
+      <c r="G115" s="32">
+        <f>IF($A115="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A115)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="58" t="n"/>
@@ -9999,6 +10469,10 @@
         <f>IF($A116="","",$A116&amp;"|"&amp;COUNTIF($A$3:$A116,$A116))</f>
         <v/>
       </c>
+      <c r="G116" s="32">
+        <f>IF($A116="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A116)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="58" t="n"/>
@@ -10010,6 +10484,10 @@
         <f>IF($A117="","",$A117&amp;"|"&amp;COUNTIF($A$3:$A117,$A117))</f>
         <v/>
       </c>
+      <c r="G117" s="32">
+        <f>IF($A117="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A117)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="58" t="n"/>
@@ -10021,6 +10499,10 @@
         <f>IF($A118="","",$A118&amp;"|"&amp;COUNTIF($A$3:$A118,$A118))</f>
         <v/>
       </c>
+      <c r="G118" s="32">
+        <f>IF($A118="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A118)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="58" t="n"/>
@@ -10032,6 +10514,10 @@
         <f>IF($A119="","",$A119&amp;"|"&amp;COUNTIF($A$3:$A119,$A119))</f>
         <v/>
       </c>
+      <c r="G119" s="32">
+        <f>IF($A119="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A119)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="58" t="n"/>
@@ -10043,6 +10529,10 @@
         <f>IF($A120="","",$A120&amp;"|"&amp;COUNTIF($A$3:$A120,$A120))</f>
         <v/>
       </c>
+      <c r="G120" s="32">
+        <f>IF($A120="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A120)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="58" t="n"/>
@@ -10054,6 +10544,10 @@
         <f>IF($A121="","",$A121&amp;"|"&amp;COUNTIF($A$3:$A121,$A121))</f>
         <v/>
       </c>
+      <c r="G121" s="32">
+        <f>IF($A121="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A121)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="58" t="n"/>
@@ -10065,6 +10559,10 @@
         <f>IF($A122="","",$A122&amp;"|"&amp;COUNTIF($A$3:$A122,$A122))</f>
         <v/>
       </c>
+      <c r="G122" s="32">
+        <f>IF($A122="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A122)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="58" t="n"/>
@@ -10076,6 +10574,10 @@
         <f>IF($A123="","",$A123&amp;"|"&amp;COUNTIF($A$3:$A123,$A123))</f>
         <v/>
       </c>
+      <c r="G123" s="32">
+        <f>IF($A123="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A123)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="58" t="n"/>
@@ -10087,6 +10589,10 @@
         <f>IF($A124="","",$A124&amp;"|"&amp;COUNTIF($A$3:$A124,$A124))</f>
         <v/>
       </c>
+      <c r="G124" s="32">
+        <f>IF($A124="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A124)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="58" t="n"/>
@@ -10098,6 +10604,10 @@
         <f>IF($A125="","",$A125&amp;"|"&amp;COUNTIF($A$3:$A125,$A125))</f>
         <v/>
       </c>
+      <c r="G125" s="32">
+        <f>IF($A125="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A125)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="58" t="n"/>
@@ -10109,6 +10619,10 @@
         <f>IF($A126="","",$A126&amp;"|"&amp;COUNTIF($A$3:$A126,$A126))</f>
         <v/>
       </c>
+      <c r="G126" s="32">
+        <f>IF($A126="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A126)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="58" t="n"/>
@@ -10120,6 +10634,10 @@
         <f>IF($A127="","",$A127&amp;"|"&amp;COUNTIF($A$3:$A127,$A127))</f>
         <v/>
       </c>
+      <c r="G127" s="32">
+        <f>IF($A127="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A127)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="58" t="n"/>
@@ -10131,6 +10649,10 @@
         <f>IF($A128="","",$A128&amp;"|"&amp;COUNTIF($A$3:$A128,$A128))</f>
         <v/>
       </c>
+      <c r="G128" s="32">
+        <f>IF($A128="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A128)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="58" t="n"/>
@@ -10142,6 +10664,10 @@
         <f>IF($A129="","",$A129&amp;"|"&amp;COUNTIF($A$3:$A129,$A129))</f>
         <v/>
       </c>
+      <c r="G129" s="32">
+        <f>IF($A129="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A129)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="58" t="n"/>
@@ -10153,6 +10679,10 @@
         <f>IF($A130="","",$A130&amp;"|"&amp;COUNTIF($A$3:$A130,$A130))</f>
         <v/>
       </c>
+      <c r="G130" s="32">
+        <f>IF($A130="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A130)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="58" t="n"/>
@@ -10164,6 +10694,10 @@
         <f>IF($A131="","",$A131&amp;"|"&amp;COUNTIF($A$3:$A131,$A131))</f>
         <v/>
       </c>
+      <c r="G131" s="32">
+        <f>IF($A131="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A131)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="58" t="n"/>
@@ -10175,6 +10709,10 @@
         <f>IF($A132="","",$A132&amp;"|"&amp;COUNTIF($A$3:$A132,$A132))</f>
         <v/>
       </c>
+      <c r="G132" s="32">
+        <f>IF($A132="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A132)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="58" t="n"/>
@@ -10186,6 +10724,10 @@
         <f>IF($A133="","",$A133&amp;"|"&amp;COUNTIF($A$3:$A133,$A133))</f>
         <v/>
       </c>
+      <c r="G133" s="32">
+        <f>IF($A133="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A133)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="58" t="n"/>
@@ -10197,6 +10739,10 @@
         <f>IF($A134="","",$A134&amp;"|"&amp;COUNTIF($A$3:$A134,$A134))</f>
         <v/>
       </c>
+      <c r="G134" s="32">
+        <f>IF($A134="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A134)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="58" t="n"/>
@@ -10208,6 +10754,10 @@
         <f>IF($A135="","",$A135&amp;"|"&amp;COUNTIF($A$3:$A135,$A135))</f>
         <v/>
       </c>
+      <c r="G135" s="32">
+        <f>IF($A135="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A135)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="58" t="n"/>
@@ -10219,6 +10769,10 @@
         <f>IF($A136="","",$A136&amp;"|"&amp;COUNTIF($A$3:$A136,$A136))</f>
         <v/>
       </c>
+      <c r="G136" s="32">
+        <f>IF($A136="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A136)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="58" t="n"/>
@@ -10230,6 +10784,10 @@
         <f>IF($A137="","",$A137&amp;"|"&amp;COUNTIF($A$3:$A137,$A137))</f>
         <v/>
       </c>
+      <c r="G137" s="32">
+        <f>IF($A137="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A137)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="58" t="n"/>
@@ -10241,6 +10799,10 @@
         <f>IF($A138="","",$A138&amp;"|"&amp;COUNTIF($A$3:$A138,$A138))</f>
         <v/>
       </c>
+      <c r="G138" s="32">
+        <f>IF($A138="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A138)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="58" t="n"/>
@@ -10252,6 +10814,10 @@
         <f>IF($A139="","",$A139&amp;"|"&amp;COUNTIF($A$3:$A139,$A139))</f>
         <v/>
       </c>
+      <c r="G139" s="32">
+        <f>IF($A139="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A139)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="58" t="n"/>
@@ -10263,6 +10829,10 @@
         <f>IF($A140="","",$A140&amp;"|"&amp;COUNTIF($A$3:$A140,$A140))</f>
         <v/>
       </c>
+      <c r="G140" s="32">
+        <f>IF($A140="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A140)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="58" t="n"/>
@@ -10274,6 +10844,10 @@
         <f>IF($A141="","",$A141&amp;"|"&amp;COUNTIF($A$3:$A141,$A141))</f>
         <v/>
       </c>
+      <c r="G141" s="32">
+        <f>IF($A141="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A141)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="58" t="n"/>
@@ -10285,6 +10859,10 @@
         <f>IF($A142="","",$A142&amp;"|"&amp;COUNTIF($A$3:$A142,$A142))</f>
         <v/>
       </c>
+      <c r="G142" s="32">
+        <f>IF($A142="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A142)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="58" t="n"/>
@@ -10296,6 +10874,10 @@
         <f>IF($A143="","",$A143&amp;"|"&amp;COUNTIF($A$3:$A143,$A143))</f>
         <v/>
       </c>
+      <c r="G143" s="32">
+        <f>IF($A143="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A143)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="58" t="n"/>
@@ -10307,6 +10889,10 @@
         <f>IF($A144="","",$A144&amp;"|"&amp;COUNTIF($A$3:$A144,$A144))</f>
         <v/>
       </c>
+      <c r="G144" s="32">
+        <f>IF($A144="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A144)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="58" t="n"/>
@@ -10318,6 +10904,10 @@
         <f>IF($A145="","",$A145&amp;"|"&amp;COUNTIF($A$3:$A145,$A145))</f>
         <v/>
       </c>
+      <c r="G145" s="32">
+        <f>IF($A145="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A145)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="58" t="n"/>
@@ -10329,6 +10919,10 @@
         <f>IF($A146="","",$A146&amp;"|"&amp;COUNTIF($A$3:$A146,$A146))</f>
         <v/>
       </c>
+      <c r="G146" s="32">
+        <f>IF($A146="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A146)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="58" t="n"/>
@@ -10340,6 +10934,10 @@
         <f>IF($A147="","",$A147&amp;"|"&amp;COUNTIF($A$3:$A147,$A147))</f>
         <v/>
       </c>
+      <c r="G147" s="32">
+        <f>IF($A147="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A147)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="58" t="n"/>
@@ -10351,6 +10949,10 @@
         <f>IF($A148="","",$A148&amp;"|"&amp;COUNTIF($A$3:$A148,$A148))</f>
         <v/>
       </c>
+      <c r="G148" s="32">
+        <f>IF($A148="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A148)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="58" t="n"/>
@@ -10362,6 +10964,10 @@
         <f>IF($A149="","",$A149&amp;"|"&amp;COUNTIF($A$3:$A149,$A149))</f>
         <v/>
       </c>
+      <c r="G149" s="32">
+        <f>IF($A149="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A149)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="58" t="n"/>
@@ -10373,6 +10979,10 @@
         <f>IF($A150="","",$A150&amp;"|"&amp;COUNTIF($A$3:$A150,$A150))</f>
         <v/>
       </c>
+      <c r="G150" s="32">
+        <f>IF($A150="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A150)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="58" t="n"/>
@@ -10384,6 +10994,10 @@
         <f>IF($A151="","",$A151&amp;"|"&amp;COUNTIF($A$3:$A151,$A151))</f>
         <v/>
       </c>
+      <c r="G151" s="32">
+        <f>IF($A151="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A151)=0,"⚠ שם קבוצה לא מוכר",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="58" t="n"/>
@@ -10393,6 +11007,10 @@
       <c r="E152" s="62" t="n"/>
       <c r="F152" s="63">
         <f>IF($A152="","",$A152&amp;"|"&amp;COUNTIF($A$3:$A152,$A152))</f>
+        <v/>
+      </c>
+      <c r="G152" s="32">
+        <f>IF($A152="","",IF(COUNTIF('קבוצות'!$A$3:$A$8,$A152)=0,"⚠ שם קבוצה לא מוכר",""))</f>
         <v/>
       </c>
     </row>

--- a/shabbat-planner.xlsx
+++ b/shabbat-planner.xlsx
@@ -11274,14 +11274,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -11304,15 +11305,20 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
+          <t>חבילת אחריות</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
           <t>חניכים (מחושב מגיליון «חניכים»)</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>ערכת צבע</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>מס' חניכים</t>
         </is>
@@ -11325,16 +11331,17 @@
         </is>
       </c>
       <c r="B3" s="86" t="n"/>
-      <c r="C3" s="87">
+      <c r="C3" s="69" t="n"/>
+      <c r="D3" s="87">
         <f>IF($A3="","",'חניכים'!$F$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D3" s="69" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>ורוד</t>
         </is>
       </c>
-      <c r="E3" s="88">
+      <c r="F3" s="88">
         <f>IF($A3="","",COUNTIF('חניכים'!$B$3:$B$132,$A3))</f>
         <v/>
       </c>
@@ -11346,16 +11353,17 @@
         </is>
       </c>
       <c r="B4" s="86" t="n"/>
-      <c r="C4" s="87">
+      <c r="C4" s="69" t="n"/>
+      <c r="D4" s="87">
         <f>IF($A4="","",'חניכים'!$G$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D4" s="69" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>ים</t>
         </is>
       </c>
-      <c r="E4" s="88">
+      <c r="F4" s="88">
         <f>IF($A4="","",COUNTIF('חניכים'!$B$3:$B$132,$A4))</f>
         <v/>
       </c>
@@ -11367,16 +11375,17 @@
         </is>
       </c>
       <c r="B5" s="86" t="n"/>
-      <c r="C5" s="87">
+      <c r="C5" s="69" t="n"/>
+      <c r="D5" s="87">
         <f>IF($A5="","",'חניכים'!$H$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D5" s="69" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>ספארי</t>
         </is>
       </c>
-      <c r="E5" s="88">
+      <c r="F5" s="88">
         <f>IF($A5="","",COUNTIF('חניכים'!$B$3:$B$132,$A5))</f>
         <v/>
       </c>
@@ -11388,16 +11397,17 @@
         </is>
       </c>
       <c r="B6" s="86" t="n"/>
-      <c r="C6" s="87">
+      <c r="C6" s="69" t="n"/>
+      <c r="D6" s="87">
         <f>IF($A6="","",'חניכים'!$I$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D6" s="69" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>שדה</t>
         </is>
       </c>
-      <c r="E6" s="88">
+      <c r="F6" s="88">
         <f>IF($A6="","",COUNTIF('חניכים'!$B$3:$B$132,$A6))</f>
         <v/>
       </c>
@@ -11405,16 +11415,17 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="80" t="n"/>
       <c r="B7" s="86" t="n"/>
-      <c r="C7" s="87">
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="87">
         <f>IF($A7="","",'חניכים'!$J$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D7" s="69" t="inlineStr">
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>סגול</t>
         </is>
       </c>
-      <c r="E7" s="88">
+      <c r="F7" s="88">
         <f>IF($A7="","",COUNTIF('חניכים'!$B$3:$B$132,$A7))</f>
         <v/>
       </c>
@@ -11422,16 +11433,17 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="80" t="n"/>
       <c r="B8" s="86" t="n"/>
-      <c r="C8" s="87">
+      <c r="C8" s="69" t="n"/>
+      <c r="D8" s="87">
         <f>IF($A8="","",'חניכים'!$K$132&amp;"")</f>
         <v/>
       </c>
-      <c r="D8" s="69" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>ירוק</t>
         </is>
       </c>
-      <c r="E8" s="88">
+      <c r="F8" s="88">
         <f>IF($A8="","",COUNTIF('חניכים'!$B$3:$B$132,$A8))</f>
         <v/>
       </c>
@@ -11439,17 +11451,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>שמות הקבוצות והמובילים נקבעים כאן. רשימת החניכים מחושבת מגיליון «חניכים» — אין מה להקליד בה. ערכת הצבע קובעת את צבע הכרטיסייה.</t>
+          <t>שמות הקבוצות והמובילים נקבעים כאן. «חבילת אחריות» היא תחום האחריות של הקבוצה בשבת הזו. רשימת החניכים מחושבת מגיליון «חניכים» — אין מה להקליד בה. ערכת הצבע קובעת את צבע הכרטיסייה.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ורוד,ים,ספארי,שדה,סגול,ירוק"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21812,7 +21824,7 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="26">
-        <f>IF('קבוצות'!$C$3="","",'קבוצות'!$C$3)</f>
+        <f>IF('קבוצות'!$D$3="","",'קבוצות'!$D$3)</f>
         <v/>
       </c>
     </row>
@@ -22637,7 +22649,7 @@
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="37">
-        <f>IF('קבוצות'!$C$4="","",'קבוצות'!$C$4)</f>
+        <f>IF('קבוצות'!$D$4="","",'קבוצות'!$D$4)</f>
         <v/>
       </c>
     </row>
@@ -23462,7 +23474,7 @@
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="41">
-        <f>IF('קבוצות'!$C$5="","",'קבוצות'!$C$5)</f>
+        <f>IF('קבוצות'!$D$5="","",'קבוצות'!$D$5)</f>
         <v/>
       </c>
     </row>
@@ -24287,7 +24299,7 @@
     </row>
     <row r="77" ht="60" customHeight="1">
       <c r="A77" s="45">
-        <f>IF('קבוצות'!$C$6="","",'קבוצות'!$C$6)</f>
+        <f>IF('קבוצות'!$D$6="","",'קבוצות'!$D$6)</f>
         <v/>
       </c>
     </row>
@@ -25112,7 +25124,7 @@
     </row>
     <row r="102" ht="60" customHeight="1">
       <c r="A102" s="49">
-        <f>IF('קבוצות'!$C$7="","",'קבוצות'!$C$7)</f>
+        <f>IF('קבוצות'!$D$7="","",'קבוצות'!$D$7)</f>
         <v/>
       </c>
     </row>
@@ -25937,7 +25949,7 @@
     </row>
     <row r="127" ht="60" customHeight="1">
       <c r="A127" s="53">
-        <f>IF('קבוצות'!$C$8="","",'קבוצות'!$C$8)</f>
+        <f>IF('קבוצות'!$D$8="","",'קבוצות'!$D$8)</f>
         <v/>
       </c>
     </row>
@@ -26897,362 +26909,362 @@
   </mergeCells>
   <conditionalFormatting sqref="A2:F3">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="2">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="3">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="10" dxfId="4">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="13" dxfId="5">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="16" dxfId="6">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A22">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="2">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="3">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="4">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="5">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="17" dxfId="6">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:F1">
     <cfRule type="expression" priority="3" dxfId="7">
-      <formula>'קבוצות'!$D$3="ורוד"</formula>
+      <formula>'קבוצות'!$E$3="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="8">
-      <formula>'קבוצות'!$D$3="ים"</formula>
+      <formula>'קבוצות'!$E$3="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="9">
-      <formula>'קבוצות'!$D$3="ספארי"</formula>
+      <formula>'קבוצות'!$E$3="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="10">
-      <formula>'קבוצות'!$D$3="שדה"</formula>
+      <formula>'קבוצות'!$E$3="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="11">
-      <formula>'קבוצות'!$D$3="סגול"</formula>
+      <formula>'קבוצות'!$E$3="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="18" dxfId="12">
-      <formula>'קבוצות'!$D$3="ירוק"</formula>
+      <formula>'קבוצות'!$E$3="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27:F28">
     <cfRule type="expression" priority="19" dxfId="1">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="22" dxfId="2">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="25" dxfId="3">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="28" dxfId="4">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="31" dxfId="5">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="34" dxfId="6">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:A47">
     <cfRule type="expression" priority="20" dxfId="1">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="23" dxfId="2">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="26" dxfId="3">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="29" dxfId="4">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="32" dxfId="5">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="35" dxfId="6">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26:F26">
     <cfRule type="expression" priority="21" dxfId="7">
-      <formula>'קבוצות'!$D$4="ורוד"</formula>
+      <formula>'קבוצות'!$E$4="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="24" dxfId="8">
-      <formula>'קבוצות'!$D$4="ים"</formula>
+      <formula>'קבוצות'!$E$4="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="27" dxfId="9">
-      <formula>'קבוצות'!$D$4="ספארי"</formula>
+      <formula>'קבוצות'!$E$4="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="30" dxfId="10">
-      <formula>'קבוצות'!$D$4="שדה"</formula>
+      <formula>'קבוצות'!$E$4="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="33" dxfId="11">
-      <formula>'קבוצות'!$D$4="סגול"</formula>
+      <formula>'קבוצות'!$E$4="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="36" dxfId="12">
-      <formula>'קבוצות'!$D$4="ירוק"</formula>
+      <formula>'קבוצות'!$E$4="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:F53">
     <cfRule type="expression" priority="37" dxfId="1">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="40" dxfId="2">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="43" dxfId="3">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="46" dxfId="4">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="49" dxfId="5">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="52" dxfId="6">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55:A72">
     <cfRule type="expression" priority="38" dxfId="1">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="41" dxfId="2">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="44" dxfId="3">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="47" dxfId="4">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="50" dxfId="5">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="53" dxfId="6">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:F51">
     <cfRule type="expression" priority="39" dxfId="7">
-      <formula>'קבוצות'!$D$5="ורוד"</formula>
+      <formula>'קבוצות'!$E$5="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="42" dxfId="8">
-      <formula>'קבוצות'!$D$5="ים"</formula>
+      <formula>'קבוצות'!$E$5="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="45" dxfId="9">
-      <formula>'קבוצות'!$D$5="ספארי"</formula>
+      <formula>'קבוצות'!$E$5="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="48" dxfId="10">
-      <formula>'קבוצות'!$D$5="שדה"</formula>
+      <formula>'קבוצות'!$E$5="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="51" dxfId="11">
-      <formula>'קבוצות'!$D$5="סגול"</formula>
+      <formula>'קבוצות'!$E$5="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="54" dxfId="12">
-      <formula>'קבוצות'!$D$5="ירוק"</formula>
+      <formula>'קבוצות'!$E$5="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:F78">
     <cfRule type="expression" priority="55" dxfId="1">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="58" dxfId="2">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="61" dxfId="3">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="64" dxfId="4">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="67" dxfId="5">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="70" dxfId="6">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A80:A97">
     <cfRule type="expression" priority="56" dxfId="1">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="59" dxfId="2">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="62" dxfId="3">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="65" dxfId="4">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="68" dxfId="5">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="71" dxfId="6">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:F76">
     <cfRule type="expression" priority="57" dxfId="7">
-      <formula>'קבוצות'!$D$6="ורוד"</formula>
+      <formula>'קבוצות'!$E$6="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="60" dxfId="8">
-      <formula>'קבוצות'!$D$6="ים"</formula>
+      <formula>'קבוצות'!$E$6="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="63" dxfId="9">
-      <formula>'קבוצות'!$D$6="ספארי"</formula>
+      <formula>'קבוצות'!$E$6="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="66" dxfId="10">
-      <formula>'קבוצות'!$D$6="שדה"</formula>
+      <formula>'קבוצות'!$E$6="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="69" dxfId="11">
-      <formula>'קבוצות'!$D$6="סגול"</formula>
+      <formula>'קבוצות'!$E$6="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="72" dxfId="12">
-      <formula>'קבוצות'!$D$6="ירוק"</formula>
+      <formula>'קבוצות'!$E$6="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:F103">
     <cfRule type="expression" priority="73" dxfId="1">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="76" dxfId="2">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="79" dxfId="3">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="82" dxfId="4">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="85" dxfId="5">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="88" dxfId="6">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A105:A122">
     <cfRule type="expression" priority="74" dxfId="1">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="77" dxfId="2">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="80" dxfId="3">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="83" dxfId="4">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="86" dxfId="5">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="89" dxfId="6">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A101:F101">
     <cfRule type="expression" priority="75" dxfId="7">
-      <formula>'קבוצות'!$D$7="ורוד"</formula>
+      <formula>'קבוצות'!$E$7="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="78" dxfId="8">
-      <formula>'קבוצות'!$D$7="ים"</formula>
+      <formula>'קבוצות'!$E$7="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="81" dxfId="9">
-      <formula>'קבוצות'!$D$7="ספארי"</formula>
+      <formula>'קבוצות'!$E$7="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="84" dxfId="10">
-      <formula>'קבוצות'!$D$7="שדה"</formula>
+      <formula>'קבוצות'!$E$7="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="87" dxfId="11">
-      <formula>'קבוצות'!$D$7="סגול"</formula>
+      <formula>'קבוצות'!$E$7="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="90" dxfId="12">
-      <formula>'קבוצות'!$D$7="ירוק"</formula>
+      <formula>'קבוצות'!$E$7="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A127:F128">
     <cfRule type="expression" priority="91" dxfId="1">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="94" dxfId="2">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="97" dxfId="3">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="100" dxfId="4">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="103" dxfId="5">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="106" dxfId="6">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A130:A147">
     <cfRule type="expression" priority="92" dxfId="1">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="95" dxfId="2">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="98" dxfId="3">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="101" dxfId="4">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="104" dxfId="5">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="107" dxfId="6">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:F126">
     <cfRule type="expression" priority="93" dxfId="7">
-      <formula>'קבוצות'!$D$8="ורוד"</formula>
+      <formula>'קבוצות'!$E$8="ורוד"</formula>
     </cfRule>
     <cfRule type="expression" priority="96" dxfId="8">
-      <formula>'קבוצות'!$D$8="ים"</formula>
+      <formula>'קבוצות'!$E$8="ים"</formula>
     </cfRule>
     <cfRule type="expression" priority="99" dxfId="9">
-      <formula>'קבוצות'!$D$8="ספארי"</formula>
+      <formula>'קבוצות'!$E$8="ספארי"</formula>
     </cfRule>
     <cfRule type="expression" priority="102" dxfId="10">
-      <formula>'קבוצות'!$D$8="שדה"</formula>
+      <formula>'קבוצות'!$E$8="שדה"</formula>
     </cfRule>
     <cfRule type="expression" priority="105" dxfId="11">
-      <formula>'קבוצות'!$D$8="סגול"</formula>
+      <formula>'קבוצות'!$E$8="סגול"</formula>
     </cfRule>
     <cfRule type="expression" priority="108" dxfId="12">
-      <formula>'קבוצות'!$D$8="ירוק"</formula>
+      <formula>'קבוצות'!$E$8="ירוק"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/shabbat-planner.xlsx
+++ b/shabbat-planner.xlsx
@@ -368,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
@@ -628,6 +628,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
@@ -14599,7 +14602,7 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="B8" s="86" t="n"/>
@@ -14625,7 +14628,7 @@
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · טיש</t>
+          <t>בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="B9" s="86" t="n"/>
@@ -14651,7 +14654,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="80" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · צהריים בשבת</t>
         </is>
       </c>
       <c r="B10" s="86" t="n"/>
@@ -14675,24 +14678,16 @@
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="80" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
+      <c r="A11" s="80" t="n"/>
       <c r="B11" s="86" t="n"/>
-      <c r="C11" s="69" t="inlineStr">
-        <is>
-          <t>בית מדרש ופינת קפה</t>
-        </is>
-      </c>
+      <c r="C11" s="69" t="n"/>
       <c r="D11" s="87">
         <f>IF($A11="","",'חניכים'!$N$132&amp;"")</f>
         <v/>
       </c>
       <c r="E11" s="69" t="inlineStr">
         <is>
-          <t>ים</t>
+          <t>ספארי</t>
         </is>
       </c>
       <c r="F11" s="88">
@@ -14783,14 +14778,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -14823,6 +14819,11 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
+          <t>שעה</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
           <t>עוגן בלו"ז</t>
         </is>
       </c>
@@ -14848,7 +14849,8 @@
           <t>הכנת בצקים לעוגות ולחלות</t>
         </is>
       </c>
-      <c r="E3" s="76" t="inlineStr">
+      <c r="E3" s="90" t="n"/>
+      <c r="F3" s="76" t="inlineStr">
         <is>
           <t>חמישי — הכנות</t>
         </is>
@@ -14875,7 +14877,8 @@
           <t>אפיית חלות</t>
         </is>
       </c>
-      <c r="E4" s="76" t="inlineStr">
+      <c r="E4" s="90" t="n"/>
+      <c r="F4" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -14902,7 +14905,8 @@
           <t>אפיית לחמניות</t>
         </is>
       </c>
-      <c r="E5" s="76" t="inlineStr">
+      <c r="E5" s="90" t="n"/>
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -14929,7 +14933,8 @@
           <t>בייגל בייטס</t>
         </is>
       </c>
-      <c r="E6" s="76" t="inlineStr">
+      <c r="E6" s="90" t="n"/>
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -14956,7 +14961,8 @@
           <t>פנקייקים</t>
         </is>
       </c>
-      <c r="E7" s="76" t="inlineStr">
+      <c r="E7" s="90" t="n"/>
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -14983,7 +14989,8 @@
           <t>עוגות שמרים</t>
         </is>
       </c>
-      <c r="E8" s="76" t="inlineStr">
+      <c r="E8" s="90" t="n"/>
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15010,7 +15017,8 @@
           <t>עוגות בננה עם שוקו צ'יפס</t>
         </is>
       </c>
-      <c r="E9" s="76" t="inlineStr">
+      <c r="E9" s="90" t="n"/>
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15037,7 +15045,8 @@
           <t>עוגות גזר</t>
         </is>
       </c>
-      <c r="E10" s="76" t="inlineStr">
+      <c r="E10" s="90" t="n"/>
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15064,7 +15073,8 @@
           <t>עוגת ביסקוויטים גבינה</t>
         </is>
       </c>
-      <c r="E11" s="76" t="inlineStr">
+      <c r="E11" s="90" t="n"/>
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15091,7 +15101,8 @@
           <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
-      <c r="E12" s="76" t="inlineStr">
+      <c r="E12" s="90" t="n"/>
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15118,7 +15129,8 @@
           <t>כדורי שוקולד פרווה</t>
         </is>
       </c>
-      <c r="E13" s="76" t="inlineStr">
+      <c r="E13" s="90" t="n"/>
+      <c r="F13" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15142,10 +15154,11 @@
       </c>
       <c r="D14" s="68" t="inlineStr">
         <is>
-          <t>עוגות לסעודה שלישית</t>
-        </is>
-      </c>
-      <c r="E14" s="76" t="inlineStr">
+          <t>עוגות פרווה לטיש</t>
+        </is>
+      </c>
+      <c r="E14" s="90" t="n"/>
+      <c r="F14" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15159,7 +15172,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>בישול</t>
+          <t>מאפים</t>
         </is>
       </c>
       <c r="C15" s="76" t="inlineStr">
@@ -15169,10 +15182,11 @@
       </c>
       <c r="D15" s="68" t="inlineStr">
         <is>
-          <t>סלטים לארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="E15" s="76" t="inlineStr">
+          <t>עוגות לסעודה שלישית</t>
+        </is>
+      </c>
+      <c r="E15" s="90" t="n"/>
+      <c r="F15" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15196,10 +15210,11 @@
       </c>
       <c r="D16" s="68" t="inlineStr">
         <is>
-          <t>סלטים לארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="E16" s="76" t="inlineStr">
+          <t>סלטים לארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="E16" s="90" t="n"/>
+      <c r="F16" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15223,10 +15238,11 @@
       </c>
       <c r="D17" s="68" t="inlineStr">
         <is>
-          <t>סלט ביצים</t>
-        </is>
-      </c>
-      <c r="E17" s="76" t="inlineStr">
+          <t>סלטים לארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="E17" s="90" t="n"/>
+      <c r="F17" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15250,10 +15266,11 @@
       </c>
       <c r="D18" s="68" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
-        </is>
-      </c>
-      <c r="E18" s="76" t="inlineStr">
+          <t>סלט ביצים</t>
+        </is>
+      </c>
+      <c r="E18" s="90" t="n"/>
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15277,10 +15294,11 @@
       </c>
       <c r="D19" s="68" t="inlineStr">
         <is>
-          <t>חיתוך ירקות לסלט</t>
-        </is>
-      </c>
-      <c r="E19" s="76" t="inlineStr">
+          <t>מטבוחה</t>
+        </is>
+      </c>
+      <c r="E19" s="90" t="n"/>
+      <c r="F19" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
@@ -15299,2635 +15317,2804 @@
       </c>
       <c r="C20" s="76" t="inlineStr">
         <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D20" s="68" t="inlineStr">
+        <is>
+          <t>חיתוך ירקות לסלט</t>
+        </is>
+      </c>
+      <c r="E20" s="90" t="n"/>
+      <c r="F20" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת בוקר שישי</t>
+        </is>
+      </c>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D21" s="68" t="inlineStr">
+        <is>
+          <t>הכנת ארוחת בוקר שישי וניקיון אחריה</t>
+        </is>
+      </c>
+      <c r="E21" s="90" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="F21" s="76" t="inlineStr">
+        <is>
+          <t>שישי — ארוחת בוקר</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שישי</t>
+        </is>
+      </c>
+      <c r="C22" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D22" s="68" t="inlineStr">
+        <is>
+          <t>הכנת ארוחת צהריים שישי וניקיון אחריה</t>
+        </is>
+      </c>
+      <c r="E22" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F22" s="76" t="inlineStr">
+        <is>
+          <t>שישי — ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C23" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D23" s="68" t="inlineStr">
+        <is>
+          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+        </is>
+      </c>
+      <c r="E23" s="90" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F23" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C24" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D24" s="68" t="inlineStr">
+        <is>
+          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+        </is>
+      </c>
+      <c r="E24" s="90" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="F24" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C25" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D25" s="68" t="inlineStr">
+        <is>
+          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+        </is>
+      </c>
+      <c r="E25" s="90" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F25" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת ערב שבת</t>
+        </is>
+      </c>
+      <c r="C26" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D26" s="68" t="inlineStr">
+        <is>
+          <t>עריכת שולחן — טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+        </is>
+      </c>
+      <c r="E26" s="90" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F26" s="76" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C27" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D27" s="68" t="inlineStr">
+        <is>
+          <t>חימום 10 עוגות פרווה על הפלטה</t>
+        </is>
+      </c>
+      <c r="E27" s="90" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F27" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C28" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D28" s="68" t="inlineStr">
+        <is>
+          <t>חיתוך אבטיח</t>
+        </is>
+      </c>
+      <c r="E28" s="90" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F28" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C29" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D29" s="68" t="inlineStr">
+        <is>
+          <t>פריסת שולחן במרכז — 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+        </is>
+      </c>
+      <c r="E29" s="90" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="F29" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C30" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D30" s="68" t="inlineStr">
+        <is>
+          <t>סידור המרחב בחדר האוכל — שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+        </is>
+      </c>
+      <c r="E30" s="90" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="F30" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="C31" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D31" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון חדר האוכל בסיום הטיש — טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+        </is>
+      </c>
+      <c r="E31" s="90" t="n"/>
+      <c r="F31" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C32" s="76" t="inlineStr">
+        <is>
           <t>שבת</t>
         </is>
       </c>
-      <c r="D20" s="68" t="inlineStr">
-        <is>
-          <t>חיתוך פירות לקידוש</t>
-        </is>
-      </c>
-      <c r="E20" s="76" t="inlineStr">
+      <c r="D32" s="68" t="inlineStr">
+        <is>
+          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+        </is>
+      </c>
+      <c r="E32" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F32" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C33" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D33" s="68" t="inlineStr">
+        <is>
+          <t>חימום עוגות</t>
+        </is>
+      </c>
+      <c r="E33" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F33" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C34" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D34" s="68" t="inlineStr">
+        <is>
+          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+        </is>
+      </c>
+      <c r="E34" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F34" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C35" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D35" s="68" t="inlineStr">
+        <is>
+          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+        </is>
+      </c>
+      <c r="E35" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F35" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="C36" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D36" s="68" t="inlineStr">
+        <is>
+          <t>חיתוך האבטיח</t>
+        </is>
+      </c>
+      <c r="E36" s="90" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F36" s="76" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="C37" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D37" s="68" t="inlineStr">
+        <is>
+          <t>הנחת האוכל בתנור החימום</t>
+        </is>
+      </c>
+      <c r="E37" s="90" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="F37" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="C38" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D38" s="68" t="inlineStr">
+        <is>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+        </is>
+      </c>
+      <c r="E38" s="90" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="F38" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="C39" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D39" s="68" t="inlineStr">
+        <is>
+          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+        </is>
+      </c>
+      <c r="E39" s="90" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="F39" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+      <c r="C40" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D40" s="68" t="inlineStr">
+        <is>
+          <t>הכנסת מאפים לחימום והוצאת האוכל</t>
+        </is>
+      </c>
+      <c r="E40" s="90" t="n"/>
+      <c r="F40" s="76" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="91" t="inlineStr">
+        <is>
+          <t>תורנות ארוחה</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+      <c r="C41" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D41" s="68" t="inlineStr">
+        <is>
+          <t>עריכת המרחב וסידור בסיום</t>
+        </is>
+      </c>
+      <c r="E41" s="90" t="n"/>
+      <c r="F41" s="76" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C42" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D42" s="68" t="inlineStr">
+        <is>
+          <t>הפיכת בית מיכאל לבית כנסת — מחיצה, שורות כיסאות משני הצדדים, סידורים על הכיסאות, הפעלת מזגן</t>
+        </is>
+      </c>
+      <c r="E42" s="90" t="n"/>
+      <c r="F42" s="76" t="inlineStr">
+        <is>
+          <t>קבלת שבת וערבית</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C43" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D43" s="68" t="inlineStr">
+        <is>
+          <t>הבאת ספות וסידור מרחב הטיש</t>
+        </is>
+      </c>
+      <c r="E43" s="90" t="n"/>
+      <c r="F43" s="76" t="inlineStr">
+        <is>
+          <t>טיש עם איש צוות</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C44" s="76" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="D44" s="68" t="inlineStr">
+        <is>
+          <t>טאטוא ושטיפת בית מיכאל</t>
+        </is>
+      </c>
+      <c r="E44" s="90" t="n"/>
+      <c r="F44" s="76" t="inlineStr">
+        <is>
+          <t>ניקיונות וארגון הקמפוס</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>בית מיכאל</t>
+        </is>
+      </c>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="D45" s="68" t="inlineStr">
+        <is>
+          <t>החזרת בית המדרש לסידור המקורי</t>
+        </is>
+      </c>
+      <c r="E45" s="90" t="n"/>
+      <c r="F45" s="76" t="inlineStr">
+        <is>
+          <t>ניקיונות וארגון הקמפוס</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>חדר אוכל</t>
+        </is>
+      </c>
+      <c r="C46" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D46" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור חדר אוכל</t>
+        </is>
+      </c>
+      <c r="E46" s="90" t="n"/>
+      <c r="F46" s="76" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>חדר אוכל</t>
+        </is>
+      </c>
+      <c r="C47" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D47" s="68" t="inlineStr">
+        <is>
+          <t>שטיפת רצפת חדר האוכל</t>
+        </is>
+      </c>
+      <c r="E47" s="90" t="n"/>
+      <c r="F47" s="76" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>שירותי חדר אוכל</t>
+        </is>
+      </c>
+      <c r="C48" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D48" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון שירותי חדר אוכל</t>
+        </is>
+      </c>
+      <c r="E48" s="90" t="n"/>
+      <c r="F48" s="76" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>שירותים כלליים</t>
+        </is>
+      </c>
+      <c r="C49" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D49" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון שירותים — אקונומיקה ונייר</t>
+        </is>
+      </c>
+      <c r="E49" s="90" t="n"/>
+      <c r="F49" s="76" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>מטבח</t>
+        </is>
+      </c>
+      <c r="C50" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D50" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון מטבח — כולל הכל</t>
+        </is>
+      </c>
+      <c r="E50" s="90" t="n"/>
+      <c r="F50" s="76" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>מטבח</t>
+        </is>
+      </c>
+      <c r="C51" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D51" s="68" t="inlineStr">
+        <is>
+          <t>כיריים וכיורים</t>
+        </is>
+      </c>
+      <c r="E51" s="90" t="n"/>
+      <c r="F51" s="76" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>מטבח</t>
+        </is>
+      </c>
+      <c r="C52" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D52" s="68" t="inlineStr">
+        <is>
+          <t>פינוי כלים מהייבוש וסידור מזווה</t>
+        </is>
+      </c>
+      <c r="E52" s="90" t="n"/>
+      <c r="F52" s="76" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>חדר מקררים</t>
+        </is>
+      </c>
+      <c r="C53" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D53" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור חדר מקררים</t>
+        </is>
+      </c>
+      <c r="E53" s="90" t="n"/>
+      <c r="F53" s="76" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>קוביה</t>
+        </is>
+      </c>
+      <c r="C54" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D54" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור הקוביה</t>
+        </is>
+      </c>
+      <c r="E54" s="90" t="n"/>
+      <c r="F54" s="76" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>מרחבי חבורות</t>
+        </is>
+      </c>
+      <c r="C55" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D55" s="68" t="inlineStr">
+        <is>
+          <t>סידור מרחבי החבורות — כיסאות לפי מספר החבורות</t>
+        </is>
+      </c>
+      <c r="E55" s="90" t="n"/>
+      <c r="F55" s="76" t="inlineStr">
+        <is>
+          <t>חבורות חניכים</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>מרפסת וחצר</t>
+        </is>
+      </c>
+      <c r="C56" s="76" t="inlineStr">
+        <is>
+          <t>משתנה</t>
+        </is>
+      </c>
+      <c r="D56" s="68" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור המרפסת והחצר</t>
+        </is>
+      </c>
+      <c r="E56" s="90" t="n"/>
+      <c r="F56" s="76" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="92" t="inlineStr">
+        <is>
+          <t>ניקיון וסידור</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+      <c r="C57" s="76" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="D57" s="68" t="inlineStr">
+        <is>
+          <t>החזרת ספות ורהיטים למקומם</t>
+        </is>
+      </c>
+      <c r="E57" s="90" t="n"/>
+      <c r="F57" s="76" t="inlineStr">
+        <is>
+          <t>ניקיונות וארגון הקמפוס</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C58" s="76" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D58" s="68" t="inlineStr">
+        <is>
+          <t>הכנת פלטות חימום והדלקתן</t>
+        </is>
+      </c>
+      <c r="E58" s="90" t="n"/>
+      <c r="F58" s="76" t="inlineStr">
         <is>
           <t>שישי — הכנות ועבודה</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת בוקר שישי</t>
-        </is>
-      </c>
-      <c r="C21" s="76" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C59" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D21" s="68" t="inlineStr">
-        <is>
-          <t>הכנת ארוחת בוקר שישי וניקיון אחריה</t>
-        </is>
-      </c>
-      <c r="E21" s="76" t="inlineStr">
-        <is>
-          <t>שישי — ארוחת בוקר</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שישי</t>
-        </is>
-      </c>
-      <c r="C22" s="76" t="inlineStr">
+      <c r="D59" s="68" t="inlineStr">
+        <is>
+          <t>הדלקת תנור החימום במטבח</t>
+        </is>
+      </c>
+      <c r="E59" s="90" t="n"/>
+      <c r="F59" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C60" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D22" s="68" t="inlineStr">
-        <is>
-          <t>הכנת ארוחת צהריים שישי וניקיון אחריה</t>
-        </is>
-      </c>
-      <c r="E22" s="76" t="inlineStr">
-        <is>
-          <t>שישי — ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C23" s="76" t="inlineStr">
+      <c r="D60" s="68" t="inlineStr">
+        <is>
+          <t>מילוי והדלקת מיחמים</t>
+        </is>
+      </c>
+      <c r="E60" s="90" t="n"/>
+      <c r="F60" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>חימום</t>
+        </is>
+      </c>
+      <c r="C61" s="76" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="D61" s="68" t="inlineStr">
+        <is>
+          <t>לוודא שהאוכל על הפלטות בזמן</t>
+        </is>
+      </c>
+      <c r="E61" s="90" t="n"/>
+      <c r="F61" s="76" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>הבדלה</t>
+        </is>
+      </c>
+      <c r="C62" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D23" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת אוכל מהקייטרינג לתנור חימום — כשעתיים לפני הקידוש</t>
-        </is>
-      </c>
-      <c r="E23" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C24" s="76" t="inlineStr">
+      <c r="D62" s="68" t="inlineStr">
+        <is>
+          <t>הכנת ציוד הבדלה — נר, יין, בשמים</t>
+        </is>
+      </c>
+      <c r="E62" s="90" t="n"/>
+      <c r="F62" s="76" t="inlineStr">
+        <is>
+          <t>הבדלה</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>חשמל</t>
+        </is>
+      </c>
+      <c r="C63" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D24" s="68" t="inlineStr">
-        <is>
-          <t>הוצאת האוכל מהתנור אחרי הקידוש ולפני הסעודה</t>
-        </is>
-      </c>
-      <c r="E24" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C25" s="76" t="inlineStr">
+      <c r="D63" s="68" t="inlineStr">
+        <is>
+          <t>הדלקת אורות ומזגנים לשבת וכיוון שעון שבת</t>
+        </is>
+      </c>
+      <c r="E63" s="90" t="n"/>
+      <c r="F63" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>עיתון</t>
+        </is>
+      </c>
+      <c r="C64" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D25" s="68" t="inlineStr">
-        <is>
-          <t>ארגון סלטים והכנת טחינה לשולחנות</t>
-        </is>
-      </c>
-      <c r="E25" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C26" s="76" t="inlineStr">
+      <c r="D64" s="68" t="inlineStr">
+        <is>
+          <t>הכנת עיתון השבת והפצתו</t>
+        </is>
+      </c>
+      <c r="E64" s="90" t="n"/>
+      <c r="F64" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>מרחבים</t>
+        </is>
+      </c>
+      <c r="C65" s="76" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D26" s="68" t="inlineStr">
-        <is>
-          <t>עריכת שולחנות — כפות הגשה וחלוקת סלטים</t>
-        </is>
-      </c>
-      <c r="E26" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת ערב שבת</t>
-        </is>
-      </c>
-      <c r="C27" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D27" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי הסעודה</t>
-        </is>
-      </c>
-      <c r="E27" s="76" t="inlineStr">
-        <is>
-          <t>סעודת שבת</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C28" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D28" s="68" t="inlineStr">
-        <is>
-          <t>חימום האוכל הרלוונטי בלבד לקידוש על הפלטות</t>
-        </is>
-      </c>
-      <c r="E28" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C29" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D29" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת מאפים לתנור חימום — ללא אלומיניום מעל העוגות</t>
-        </is>
-      </c>
-      <c r="E29" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C30" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D30" s="68" t="inlineStr">
-        <is>
-          <t>תיבול סלטים לקידוש</t>
-        </is>
-      </c>
-      <c r="E30" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C31" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D31" s="68" t="inlineStr">
-        <is>
-          <t>עריכת האוכל לקידוש</t>
-        </is>
-      </c>
-      <c r="E31" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C32" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D32" s="68" t="inlineStr">
-        <is>
-          <t>סידור פינת קפה — ניקוי, חלב, קפה וסוכר</t>
-        </is>
-      </c>
-      <c r="E32" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C33" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D33" s="68" t="inlineStr">
-        <is>
-          <t>הוצאת פירות חתוכים ועוגות</t>
-        </is>
-      </c>
-      <c r="E33" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C34" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D34" s="68" t="inlineStr">
-        <is>
-          <t>הוצאת כלים וסידור שולחנות במעגל</t>
-        </is>
-      </c>
-      <c r="E34" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C35" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D35" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי הקידוש</t>
-        </is>
-      </c>
-      <c r="E35" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="C36" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D36" s="68" t="inlineStr">
-        <is>
-          <t>קיפול והכנסה למקרר בסיום — לא להשאיר אוכל פתוח</t>
-        </is>
-      </c>
-      <c r="E36" s="76" t="inlineStr">
-        <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C37" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D37" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת אוכל מהקייטרינג לתנור חימום — כשעתיים לפני ארוחת הצהריים</t>
-        </is>
-      </c>
-      <c r="E37" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C38" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D38" s="68" t="inlineStr">
-        <is>
-          <t>עריכת שולחן לארוחת צהריים אחרי הקידוש</t>
-        </is>
-      </c>
-      <c r="E38" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C39" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D39" s="68" t="inlineStr">
-        <is>
-          <t>חלוקת סלטים לשולחנות</t>
-        </is>
-      </c>
-      <c r="E39" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="C40" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D40" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מרחב האוכל אחרי ארוחת הצהריים</t>
-        </is>
-      </c>
-      <c r="E40" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-      <c r="C41" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D41" s="68" t="inlineStr">
-        <is>
-          <t>הכנסת מאפים לחימום והוצאת האוכל</t>
-        </is>
-      </c>
-      <c r="E41" s="76" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-      <c r="C42" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D42" s="68" t="inlineStr">
-        <is>
-          <t>עריכת המרחב וסידור בסיום</t>
-        </is>
-      </c>
-      <c r="E42" s="76" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C43" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D43" s="68" t="inlineStr">
-        <is>
-          <t>סידור שולחנות וכיסאות לטיש</t>
-        </is>
-      </c>
-      <c r="E43" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C44" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D44" s="68" t="inlineStr">
-        <is>
-          <t>הבאת שתייה וסידור כוסות</t>
-        </is>
-      </c>
-      <c r="E44" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C45" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D45" s="68" t="inlineStr">
-        <is>
-          <t>חימום עוגות פרווה והוצאת כיבוד</t>
-        </is>
-      </c>
-      <c r="E45" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="90" t="inlineStr">
-        <is>
-          <t>תורנות ארוחה</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="C46" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D46" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מלא בסיום הטיש</t>
-        </is>
-      </c>
-      <c r="E46" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C47" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D47" s="68" t="inlineStr">
-        <is>
-          <t>הפיכת בית מיכאל לבית כנסת — מחיצה, שורות כיסאות משני הצדדים, סידורים על הכיסאות, הפעלת מזגן</t>
-        </is>
-      </c>
-      <c r="E47" s="76" t="inlineStr">
-        <is>
-          <t>קבלת שבת וערבית</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C48" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D48" s="68" t="inlineStr">
-        <is>
-          <t>הבאת ספות וסידור מרחב הטיש</t>
-        </is>
-      </c>
-      <c r="E48" s="76" t="inlineStr">
-        <is>
-          <t>טיש עם איש צוות</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C49" s="76" t="inlineStr">
+      <c r="D65" s="68" t="inlineStr">
+        <is>
+          <t>פתיחת המרחבים והכנתם</t>
+        </is>
+      </c>
+      <c r="E65" s="90" t="n"/>
+      <c r="F65" s="76" t="inlineStr">
+        <is>
+          <t>שישי — הכנות ועבודה</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="93" t="inlineStr">
+        <is>
+          <t>אחריות טכנית</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>חשמל</t>
+        </is>
+      </c>
+      <c r="C66" s="76" t="inlineStr">
         <is>
           <t>מוצאי שבת</t>
         </is>
       </c>
-      <c r="D49" s="68" t="inlineStr">
-        <is>
-          <t>טאטוא ושטיפת בית מיכאל</t>
-        </is>
-      </c>
-      <c r="E49" s="76" t="inlineStr">
+      <c r="D66" s="68" t="inlineStr">
+        <is>
+          <t>כיבוי פלטות, מיחמים ותנור חימום</t>
+        </is>
+      </c>
+      <c r="E66" s="90" t="n"/>
+      <c r="F66" s="76" t="inlineStr">
         <is>
           <t>ניקיונות וארגון הקמפוס</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="inlineStr">
-        <is>
-          <t>בית מיכאל</t>
-        </is>
-      </c>
-      <c r="C50" s="76" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="D50" s="68" t="inlineStr">
-        <is>
-          <t>החזרת בית המדרש לסידור המקורי</t>
-        </is>
-      </c>
-      <c r="E50" s="76" t="inlineStr">
-        <is>
-          <t>ניקיונות וארגון הקמפוס</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>חדר אוכל</t>
-        </is>
-      </c>
-      <c r="C51" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D51" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור חדר אוכל</t>
-        </is>
-      </c>
-      <c r="E51" s="76" t="n"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="inlineStr">
-        <is>
-          <t>חדר אוכל</t>
-        </is>
-      </c>
-      <c r="C52" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D52" s="68" t="inlineStr">
-        <is>
-          <t>שטיפת רצפת חדר האוכל</t>
-        </is>
-      </c>
-      <c r="E52" s="76" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="inlineStr">
-        <is>
-          <t>שירותי חדר אוכל</t>
-        </is>
-      </c>
-      <c r="C53" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D53" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון שירותי חדר אוכל</t>
-        </is>
-      </c>
-      <c r="E53" s="76" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B54" s="20" t="inlineStr">
-        <is>
-          <t>שירותים כלליים</t>
-        </is>
-      </c>
-      <c r="C54" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D54" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון שירותים — אקונומיקה ונייר</t>
-        </is>
-      </c>
-      <c r="E54" s="76" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>מטבח</t>
-        </is>
-      </c>
-      <c r="C55" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D55" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון מטבח — כולל הכל</t>
-        </is>
-      </c>
-      <c r="E55" s="76" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B56" s="20" t="inlineStr">
-        <is>
-          <t>מטבח</t>
-        </is>
-      </c>
-      <c r="C56" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D56" s="68" t="inlineStr">
-        <is>
-          <t>כיריים וכיורים</t>
-        </is>
-      </c>
-      <c r="E56" s="76" t="n"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>מטבח</t>
-        </is>
-      </c>
-      <c r="C57" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D57" s="68" t="inlineStr">
-        <is>
-          <t>פינוי כלים מהייבוש וסידור מזווה</t>
-        </is>
-      </c>
-      <c r="E57" s="76" t="n"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>חדר מקררים</t>
-        </is>
-      </c>
-      <c r="C58" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D58" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור חדר מקררים</t>
-        </is>
-      </c>
-      <c r="E58" s="76" t="n"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
-        <is>
-          <t>קוביה</t>
-        </is>
-      </c>
-      <c r="C59" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D59" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור הקוביה</t>
-        </is>
-      </c>
-      <c r="E59" s="76" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>מרחבי חבורות</t>
-        </is>
-      </c>
-      <c r="C60" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D60" s="68" t="inlineStr">
-        <is>
-          <t>סידור מרחבי החבורות — כיסאות לפי מספר החבורות</t>
-        </is>
-      </c>
-      <c r="E60" s="76" t="inlineStr">
-        <is>
-          <t>חבורות חניכים</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>מרפסת וחצר</t>
-        </is>
-      </c>
-      <c r="C61" s="76" t="inlineStr">
-        <is>
-          <t>משתנה</t>
-        </is>
-      </c>
-      <c r="D61" s="68" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור המרפסת והחצר</t>
-        </is>
-      </c>
-      <c r="E61" s="76" t="n"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="91" t="inlineStr">
-        <is>
-          <t>ניקיון וסידור</t>
-        </is>
-      </c>
-      <c r="B62" s="20" t="inlineStr">
-        <is>
-          <t>כללי</t>
-        </is>
-      </c>
-      <c r="C62" s="76" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="D62" s="68" t="inlineStr">
-        <is>
-          <t>החזרת ספות ורהיטים למקומם</t>
-        </is>
-      </c>
-      <c r="E62" s="76" t="inlineStr">
-        <is>
-          <t>ניקיונות וארגון הקמפוס</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C63" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D63" s="68" t="inlineStr">
-        <is>
-          <t>הכנת פלטות חימום והדלקתן</t>
-        </is>
-      </c>
-      <c r="E63" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B64" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C64" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D64" s="68" t="inlineStr">
-        <is>
-          <t>הדלקת תנור החימום במטבח</t>
-        </is>
-      </c>
-      <c r="E64" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B65" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C65" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D65" s="68" t="inlineStr">
-        <is>
-          <t>מילוי והדלקת מיחמים</t>
-        </is>
-      </c>
-      <c r="E65" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B66" s="20" t="inlineStr">
-        <is>
-          <t>חימום</t>
-        </is>
-      </c>
-      <c r="C66" s="76" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="D66" s="68" t="inlineStr">
-        <is>
-          <t>לוודא שהאוכל על הפלטות בזמן</t>
-        </is>
-      </c>
-      <c r="E66" s="76" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-    </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B67" s="20" t="inlineStr">
-        <is>
-          <t>הבדלה</t>
-        </is>
-      </c>
-      <c r="C67" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D67" s="68" t="inlineStr">
-        <is>
-          <t>הכנת ציוד הבדלה — נר, יין, בשמים</t>
-        </is>
-      </c>
-      <c r="E67" s="76" t="inlineStr">
-        <is>
-          <t>הבדלה</t>
-        </is>
-      </c>
+      <c r="A67" s="19" t="n"/>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="76" t="n"/>
+      <c r="D67" s="68" t="n"/>
+      <c r="E67" s="90" t="n"/>
+      <c r="F67" s="76" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B68" s="20" t="inlineStr">
-        <is>
-          <t>חשמל</t>
-        </is>
-      </c>
-      <c r="C68" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D68" s="68" t="inlineStr">
-        <is>
-          <t>הדלקת אורות ומזגנים לשבת וכיוון שעון שבת</t>
-        </is>
-      </c>
-      <c r="E68" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
+      <c r="A68" s="19" t="n"/>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="76" t="n"/>
+      <c r="D68" s="68" t="n"/>
+      <c r="E68" s="90" t="n"/>
+      <c r="F68" s="76" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>עיתון</t>
-        </is>
-      </c>
-      <c r="C69" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D69" s="68" t="inlineStr">
-        <is>
-          <t>הכנת עיתון השבת והפצתו</t>
-        </is>
-      </c>
-      <c r="E69" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
+      <c r="A69" s="19" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="76" t="n"/>
+      <c r="D69" s="68" t="n"/>
+      <c r="E69" s="90" t="n"/>
+      <c r="F69" s="76" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B70" s="20" t="inlineStr">
-        <is>
-          <t>מרחבים</t>
-        </is>
-      </c>
-      <c r="C70" s="76" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D70" s="68" t="inlineStr">
-        <is>
-          <t>פתיחת המרחבים והכנתם</t>
-        </is>
-      </c>
-      <c r="E70" s="76" t="inlineStr">
-        <is>
-          <t>שישי — הכנות ועבודה</t>
-        </is>
-      </c>
+      <c r="A70" s="19" t="n"/>
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="76" t="n"/>
+      <c r="D70" s="68" t="n"/>
+      <c r="E70" s="90" t="n"/>
+      <c r="F70" s="76" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="92" t="inlineStr">
-        <is>
-          <t>אחריות טכנית</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>חשמל</t>
-        </is>
-      </c>
-      <c r="C71" s="76" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="D71" s="68" t="inlineStr">
-        <is>
-          <t>כיבוי פלטות, מיחמים ותנור חימום</t>
-        </is>
-      </c>
-      <c r="E71" s="76" t="inlineStr">
-        <is>
-          <t>ניקיונות וארגון הקמפוס</t>
-        </is>
-      </c>
+      <c r="A71" s="19" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="76" t="n"/>
+      <c r="D71" s="68" t="n"/>
+      <c r="E71" s="90" t="n"/>
+      <c r="F71" s="76" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="19" t="n"/>
       <c r="B72" s="20" t="n"/>
       <c r="C72" s="76" t="n"/>
       <c r="D72" s="68" t="n"/>
-      <c r="E72" s="76" t="n"/>
+      <c r="E72" s="90" t="n"/>
+      <c r="F72" s="76" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="19" t="n"/>
       <c r="B73" s="20" t="n"/>
       <c r="C73" s="76" t="n"/>
       <c r="D73" s="68" t="n"/>
-      <c r="E73" s="76" t="n"/>
+      <c r="E73" s="90" t="n"/>
+      <c r="F73" s="76" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="19" t="n"/>
       <c r="B74" s="20" t="n"/>
       <c r="C74" s="76" t="n"/>
       <c r="D74" s="68" t="n"/>
-      <c r="E74" s="76" t="n"/>
+      <c r="E74" s="90" t="n"/>
+      <c r="F74" s="76" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="19" t="n"/>
       <c r="B75" s="20" t="n"/>
       <c r="C75" s="76" t="n"/>
       <c r="D75" s="68" t="n"/>
-      <c r="E75" s="76" t="n"/>
+      <c r="E75" s="90" t="n"/>
+      <c r="F75" s="76" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="19" t="n"/>
       <c r="B76" s="20" t="n"/>
       <c r="C76" s="76" t="n"/>
       <c r="D76" s="68" t="n"/>
-      <c r="E76" s="76" t="n"/>
+      <c r="E76" s="90" t="n"/>
+      <c r="F76" s="76" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="19" t="n"/>
       <c r="B77" s="20" t="n"/>
       <c r="C77" s="76" t="n"/>
       <c r="D77" s="68" t="n"/>
-      <c r="E77" s="76" t="n"/>
+      <c r="E77" s="90" t="n"/>
+      <c r="F77" s="76" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="19" t="n"/>
       <c r="B78" s="20" t="n"/>
       <c r="C78" s="76" t="n"/>
       <c r="D78" s="68" t="n"/>
-      <c r="E78" s="76" t="n"/>
+      <c r="E78" s="90" t="n"/>
+      <c r="F78" s="76" t="n"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="19" t="n"/>
       <c r="B79" s="20" t="n"/>
       <c r="C79" s="76" t="n"/>
       <c r="D79" s="68" t="n"/>
-      <c r="E79" s="76" t="n"/>
+      <c r="E79" s="90" t="n"/>
+      <c r="F79" s="76" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="19" t="n"/>
       <c r="B80" s="20" t="n"/>
       <c r="C80" s="76" t="n"/>
       <c r="D80" s="68" t="n"/>
-      <c r="E80" s="76" t="n"/>
+      <c r="E80" s="90" t="n"/>
+      <c r="F80" s="76" t="n"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="19" t="n"/>
       <c r="B81" s="20" t="n"/>
       <c r="C81" s="76" t="n"/>
       <c r="D81" s="68" t="n"/>
-      <c r="E81" s="76" t="n"/>
+      <c r="E81" s="90" t="n"/>
+      <c r="F81" s="76" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="19" t="n"/>
       <c r="B82" s="20" t="n"/>
       <c r="C82" s="76" t="n"/>
       <c r="D82" s="68" t="n"/>
-      <c r="E82" s="76" t="n"/>
+      <c r="E82" s="90" t="n"/>
+      <c r="F82" s="76" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="19" t="n"/>
       <c r="B83" s="20" t="n"/>
       <c r="C83" s="76" t="n"/>
       <c r="D83" s="68" t="n"/>
-      <c r="E83" s="76" t="n"/>
+      <c r="E83" s="90" t="n"/>
+      <c r="F83" s="76" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="19" t="n"/>
       <c r="B84" s="20" t="n"/>
       <c r="C84" s="76" t="n"/>
       <c r="D84" s="68" t="n"/>
-      <c r="E84" s="76" t="n"/>
+      <c r="E84" s="90" t="n"/>
+      <c r="F84" s="76" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="19" t="n"/>
       <c r="B85" s="20" t="n"/>
       <c r="C85" s="76" t="n"/>
       <c r="D85" s="68" t="n"/>
-      <c r="E85" s="76" t="n"/>
+      <c r="E85" s="90" t="n"/>
+      <c r="F85" s="76" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="19" t="n"/>
       <c r="B86" s="20" t="n"/>
       <c r="C86" s="76" t="n"/>
       <c r="D86" s="68" t="n"/>
-      <c r="E86" s="76" t="n"/>
+      <c r="E86" s="90" t="n"/>
+      <c r="F86" s="76" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="19" t="n"/>
       <c r="B87" s="20" t="n"/>
       <c r="C87" s="76" t="n"/>
       <c r="D87" s="68" t="n"/>
-      <c r="E87" s="76" t="n"/>
+      <c r="E87" s="90" t="n"/>
+      <c r="F87" s="76" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="19" t="n"/>
       <c r="B88" s="20" t="n"/>
       <c r="C88" s="76" t="n"/>
       <c r="D88" s="68" t="n"/>
-      <c r="E88" s="76" t="n"/>
+      <c r="E88" s="90" t="n"/>
+      <c r="F88" s="76" t="n"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="19" t="n"/>
       <c r="B89" s="20" t="n"/>
       <c r="C89" s="76" t="n"/>
       <c r="D89" s="68" t="n"/>
-      <c r="E89" s="76" t="n"/>
+      <c r="E89" s="90" t="n"/>
+      <c r="F89" s="76" t="n"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="19" t="n"/>
       <c r="B90" s="20" t="n"/>
       <c r="C90" s="76" t="n"/>
       <c r="D90" s="68" t="n"/>
-      <c r="E90" s="76" t="n"/>
+      <c r="E90" s="90" t="n"/>
+      <c r="F90" s="76" t="n"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="19" t="n"/>
       <c r="B91" s="20" t="n"/>
       <c r="C91" s="76" t="n"/>
       <c r="D91" s="68" t="n"/>
-      <c r="E91" s="76" t="n"/>
+      <c r="E91" s="90" t="n"/>
+      <c r="F91" s="76" t="n"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="19" t="n"/>
       <c r="B92" s="20" t="n"/>
       <c r="C92" s="76" t="n"/>
       <c r="D92" s="68" t="n"/>
-      <c r="E92" s="76" t="n"/>
+      <c r="E92" s="90" t="n"/>
+      <c r="F92" s="76" t="n"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="19" t="n"/>
       <c r="B93" s="20" t="n"/>
       <c r="C93" s="76" t="n"/>
       <c r="D93" s="68" t="n"/>
-      <c r="E93" s="76" t="n"/>
+      <c r="E93" s="90" t="n"/>
+      <c r="F93" s="76" t="n"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="19" t="n"/>
       <c r="B94" s="20" t="n"/>
       <c r="C94" s="76" t="n"/>
       <c r="D94" s="68" t="n"/>
-      <c r="E94" s="76" t="n"/>
+      <c r="E94" s="90" t="n"/>
+      <c r="F94" s="76" t="n"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="19" t="n"/>
       <c r="B95" s="20" t="n"/>
       <c r="C95" s="76" t="n"/>
       <c r="D95" s="68" t="n"/>
-      <c r="E95" s="76" t="n"/>
+      <c r="E95" s="90" t="n"/>
+      <c r="F95" s="76" t="n"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="19" t="n"/>
       <c r="B96" s="20" t="n"/>
       <c r="C96" s="76" t="n"/>
       <c r="D96" s="68" t="n"/>
-      <c r="E96" s="76" t="n"/>
+      <c r="E96" s="90" t="n"/>
+      <c r="F96" s="76" t="n"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="19" t="n"/>
       <c r="B97" s="20" t="n"/>
       <c r="C97" s="76" t="n"/>
       <c r="D97" s="68" t="n"/>
-      <c r="E97" s="76" t="n"/>
+      <c r="E97" s="90" t="n"/>
+      <c r="F97" s="76" t="n"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="19" t="n"/>
       <c r="B98" s="20" t="n"/>
       <c r="C98" s="76" t="n"/>
       <c r="D98" s="68" t="n"/>
-      <c r="E98" s="76" t="n"/>
+      <c r="E98" s="90" t="n"/>
+      <c r="F98" s="76" t="n"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="19" t="n"/>
       <c r="B99" s="20" t="n"/>
       <c r="C99" s="76" t="n"/>
       <c r="D99" s="68" t="n"/>
-      <c r="E99" s="76" t="n"/>
+      <c r="E99" s="90" t="n"/>
+      <c r="F99" s="76" t="n"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="19" t="n"/>
       <c r="B100" s="20" t="n"/>
       <c r="C100" s="76" t="n"/>
       <c r="D100" s="68" t="n"/>
-      <c r="E100" s="76" t="n"/>
+      <c r="E100" s="90" t="n"/>
+      <c r="F100" s="76" t="n"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="19" t="n"/>
       <c r="B101" s="20" t="n"/>
       <c r="C101" s="76" t="n"/>
       <c r="D101" s="68" t="n"/>
-      <c r="E101" s="76" t="n"/>
+      <c r="E101" s="90" t="n"/>
+      <c r="F101" s="76" t="n"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="19" t="n"/>
       <c r="B102" s="20" t="n"/>
       <c r="C102" s="76" t="n"/>
       <c r="D102" s="68" t="n"/>
-      <c r="E102" s="76" t="n"/>
+      <c r="E102" s="90" t="n"/>
+      <c r="F102" s="76" t="n"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="19" t="n"/>
       <c r="B103" s="20" t="n"/>
       <c r="C103" s="76" t="n"/>
       <c r="D103" s="68" t="n"/>
-      <c r="E103" s="76" t="n"/>
+      <c r="E103" s="90" t="n"/>
+      <c r="F103" s="76" t="n"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="19" t="n"/>
       <c r="B104" s="20" t="n"/>
       <c r="C104" s="76" t="n"/>
       <c r="D104" s="68" t="n"/>
-      <c r="E104" s="76" t="n"/>
+      <c r="E104" s="90" t="n"/>
+      <c r="F104" s="76" t="n"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="19" t="n"/>
       <c r="B105" s="20" t="n"/>
       <c r="C105" s="76" t="n"/>
       <c r="D105" s="68" t="n"/>
-      <c r="E105" s="76" t="n"/>
+      <c r="E105" s="90" t="n"/>
+      <c r="F105" s="76" t="n"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="19" t="n"/>
       <c r="B106" s="20" t="n"/>
       <c r="C106" s="76" t="n"/>
       <c r="D106" s="68" t="n"/>
-      <c r="E106" s="76" t="n"/>
+      <c r="E106" s="90" t="n"/>
+      <c r="F106" s="76" t="n"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="19" t="n"/>
       <c r="B107" s="20" t="n"/>
       <c r="C107" s="76" t="n"/>
       <c r="D107" s="68" t="n"/>
-      <c r="E107" s="76" t="n"/>
+      <c r="E107" s="90" t="n"/>
+      <c r="F107" s="76" t="n"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="19" t="n"/>
       <c r="B108" s="20" t="n"/>
       <c r="C108" s="76" t="n"/>
       <c r="D108" s="68" t="n"/>
-      <c r="E108" s="76" t="n"/>
+      <c r="E108" s="90" t="n"/>
+      <c r="F108" s="76" t="n"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="19" t="n"/>
       <c r="B109" s="20" t="n"/>
       <c r="C109" s="76" t="n"/>
       <c r="D109" s="68" t="n"/>
-      <c r="E109" s="76" t="n"/>
+      <c r="E109" s="90" t="n"/>
+      <c r="F109" s="76" t="n"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="19" t="n"/>
       <c r="B110" s="20" t="n"/>
       <c r="C110" s="76" t="n"/>
       <c r="D110" s="68" t="n"/>
-      <c r="E110" s="76" t="n"/>
+      <c r="E110" s="90" t="n"/>
+      <c r="F110" s="76" t="n"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="19" t="n"/>
       <c r="B111" s="20" t="n"/>
       <c r="C111" s="76" t="n"/>
       <c r="D111" s="68" t="n"/>
-      <c r="E111" s="76" t="n"/>
+      <c r="E111" s="90" t="n"/>
+      <c r="F111" s="76" t="n"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="19" t="n"/>
       <c r="B112" s="20" t="n"/>
       <c r="C112" s="76" t="n"/>
       <c r="D112" s="68" t="n"/>
-      <c r="E112" s="76" t="n"/>
+      <c r="E112" s="90" t="n"/>
+      <c r="F112" s="76" t="n"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="19" t="n"/>
       <c r="B113" s="20" t="n"/>
       <c r="C113" s="76" t="n"/>
       <c r="D113" s="68" t="n"/>
-      <c r="E113" s="76" t="n"/>
+      <c r="E113" s="90" t="n"/>
+      <c r="F113" s="76" t="n"/>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="19" t="n"/>
       <c r="B114" s="20" t="n"/>
       <c r="C114" s="76" t="n"/>
       <c r="D114" s="68" t="n"/>
-      <c r="E114" s="76" t="n"/>
+      <c r="E114" s="90" t="n"/>
+      <c r="F114" s="76" t="n"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="19" t="n"/>
       <c r="B115" s="20" t="n"/>
       <c r="C115" s="76" t="n"/>
       <c r="D115" s="68" t="n"/>
-      <c r="E115" s="76" t="n"/>
+      <c r="E115" s="90" t="n"/>
+      <c r="F115" s="76" t="n"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="19" t="n"/>
       <c r="B116" s="20" t="n"/>
       <c r="C116" s="76" t="n"/>
       <c r="D116" s="68" t="n"/>
-      <c r="E116" s="76" t="n"/>
+      <c r="E116" s="90" t="n"/>
+      <c r="F116" s="76" t="n"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="19" t="n"/>
       <c r="B117" s="20" t="n"/>
       <c r="C117" s="76" t="n"/>
       <c r="D117" s="68" t="n"/>
-      <c r="E117" s="76" t="n"/>
+      <c r="E117" s="90" t="n"/>
+      <c r="F117" s="76" t="n"/>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="19" t="n"/>
       <c r="B118" s="20" t="n"/>
       <c r="C118" s="76" t="n"/>
       <c r="D118" s="68" t="n"/>
-      <c r="E118" s="76" t="n"/>
+      <c r="E118" s="90" t="n"/>
+      <c r="F118" s="76" t="n"/>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="19" t="n"/>
       <c r="B119" s="20" t="n"/>
       <c r="C119" s="76" t="n"/>
       <c r="D119" s="68" t="n"/>
-      <c r="E119" s="76" t="n"/>
+      <c r="E119" s="90" t="n"/>
+      <c r="F119" s="76" t="n"/>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="19" t="n"/>
       <c r="B120" s="20" t="n"/>
       <c r="C120" s="76" t="n"/>
       <c r="D120" s="68" t="n"/>
-      <c r="E120" s="76" t="n"/>
+      <c r="E120" s="90" t="n"/>
+      <c r="F120" s="76" t="n"/>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="19" t="n"/>
       <c r="B121" s="20" t="n"/>
       <c r="C121" s="76" t="n"/>
       <c r="D121" s="68" t="n"/>
-      <c r="E121" s="76" t="n"/>
+      <c r="E121" s="90" t="n"/>
+      <c r="F121" s="76" t="n"/>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="19" t="n"/>
       <c r="B122" s="20" t="n"/>
       <c r="C122" s="76" t="n"/>
       <c r="D122" s="68" t="n"/>
-      <c r="E122" s="76" t="n"/>
+      <c r="E122" s="90" t="n"/>
+      <c r="F122" s="76" t="n"/>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="19" t="n"/>
       <c r="B123" s="20" t="n"/>
       <c r="C123" s="76" t="n"/>
       <c r="D123" s="68" t="n"/>
-      <c r="E123" s="76" t="n"/>
+      <c r="E123" s="90" t="n"/>
+      <c r="F123" s="76" t="n"/>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="19" t="n"/>
       <c r="B124" s="20" t="n"/>
       <c r="C124" s="76" t="n"/>
       <c r="D124" s="68" t="n"/>
-      <c r="E124" s="76" t="n"/>
+      <c r="E124" s="90" t="n"/>
+      <c r="F124" s="76" t="n"/>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="19" t="n"/>
       <c r="B125" s="20" t="n"/>
       <c r="C125" s="76" t="n"/>
       <c r="D125" s="68" t="n"/>
-      <c r="E125" s="76" t="n"/>
+      <c r="E125" s="90" t="n"/>
+      <c r="F125" s="76" t="n"/>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="19" t="n"/>
       <c r="B126" s="20" t="n"/>
       <c r="C126" s="76" t="n"/>
       <c r="D126" s="68" t="n"/>
-      <c r="E126" s="76" t="n"/>
+      <c r="E126" s="90" t="n"/>
+      <c r="F126" s="76" t="n"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="19" t="n"/>
       <c r="B127" s="20" t="n"/>
       <c r="C127" s="76" t="n"/>
       <c r="D127" s="68" t="n"/>
-      <c r="E127" s="76" t="n"/>
+      <c r="E127" s="90" t="n"/>
+      <c r="F127" s="76" t="n"/>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="19" t="n"/>
       <c r="B128" s="20" t="n"/>
       <c r="C128" s="76" t="n"/>
       <c r="D128" s="68" t="n"/>
-      <c r="E128" s="76" t="n"/>
+      <c r="E128" s="90" t="n"/>
+      <c r="F128" s="76" t="n"/>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="19" t="n"/>
       <c r="B129" s="20" t="n"/>
       <c r="C129" s="76" t="n"/>
       <c r="D129" s="68" t="n"/>
-      <c r="E129" s="76" t="n"/>
+      <c r="E129" s="90" t="n"/>
+      <c r="F129" s="76" t="n"/>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="19" t="n"/>
       <c r="B130" s="20" t="n"/>
       <c r="C130" s="76" t="n"/>
       <c r="D130" s="68" t="n"/>
-      <c r="E130" s="76" t="n"/>
+      <c r="E130" s="90" t="n"/>
+      <c r="F130" s="76" t="n"/>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="19" t="n"/>
       <c r="B131" s="20" t="n"/>
       <c r="C131" s="76" t="n"/>
       <c r="D131" s="68" t="n"/>
-      <c r="E131" s="76" t="n"/>
+      <c r="E131" s="90" t="n"/>
+      <c r="F131" s="76" t="n"/>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="19" t="n"/>
       <c r="B132" s="20" t="n"/>
       <c r="C132" s="76" t="n"/>
       <c r="D132" s="68" t="n"/>
-      <c r="E132" s="76" t="n"/>
+      <c r="E132" s="90" t="n"/>
+      <c r="F132" s="76" t="n"/>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="19" t="n"/>
       <c r="B133" s="20" t="n"/>
       <c r="C133" s="76" t="n"/>
       <c r="D133" s="68" t="n"/>
-      <c r="E133" s="76" t="n"/>
+      <c r="E133" s="90" t="n"/>
+      <c r="F133" s="76" t="n"/>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="19" t="n"/>
       <c r="B134" s="20" t="n"/>
       <c r="C134" s="76" t="n"/>
       <c r="D134" s="68" t="n"/>
-      <c r="E134" s="76" t="n"/>
+      <c r="E134" s="90" t="n"/>
+      <c r="F134" s="76" t="n"/>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="19" t="n"/>
       <c r="B135" s="20" t="n"/>
       <c r="C135" s="76" t="n"/>
       <c r="D135" s="68" t="n"/>
-      <c r="E135" s="76" t="n"/>
+      <c r="E135" s="90" t="n"/>
+      <c r="F135" s="76" t="n"/>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="19" t="n"/>
       <c r="B136" s="20" t="n"/>
       <c r="C136" s="76" t="n"/>
       <c r="D136" s="68" t="n"/>
-      <c r="E136" s="76" t="n"/>
+      <c r="E136" s="90" t="n"/>
+      <c r="F136" s="76" t="n"/>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="19" t="n"/>
       <c r="B137" s="20" t="n"/>
       <c r="C137" s="76" t="n"/>
       <c r="D137" s="68" t="n"/>
-      <c r="E137" s="76" t="n"/>
+      <c r="E137" s="90" t="n"/>
+      <c r="F137" s="76" t="n"/>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="19" t="n"/>
       <c r="B138" s="20" t="n"/>
       <c r="C138" s="76" t="n"/>
       <c r="D138" s="68" t="n"/>
-      <c r="E138" s="76" t="n"/>
+      <c r="E138" s="90" t="n"/>
+      <c r="F138" s="76" t="n"/>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="19" t="n"/>
       <c r="B139" s="20" t="n"/>
       <c r="C139" s="76" t="n"/>
       <c r="D139" s="68" t="n"/>
-      <c r="E139" s="76" t="n"/>
+      <c r="E139" s="90" t="n"/>
+      <c r="F139" s="76" t="n"/>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="19" t="n"/>
       <c r="B140" s="20" t="n"/>
       <c r="C140" s="76" t="n"/>
       <c r="D140" s="68" t="n"/>
-      <c r="E140" s="76" t="n"/>
+      <c r="E140" s="90" t="n"/>
+      <c r="F140" s="76" t="n"/>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="19" t="n"/>
       <c r="B141" s="20" t="n"/>
       <c r="C141" s="76" t="n"/>
       <c r="D141" s="68" t="n"/>
-      <c r="E141" s="76" t="n"/>
+      <c r="E141" s="90" t="n"/>
+      <c r="F141" s="76" t="n"/>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="19" t="n"/>
       <c r="B142" s="20" t="n"/>
       <c r="C142" s="76" t="n"/>
       <c r="D142" s="68" t="n"/>
-      <c r="E142" s="76" t="n"/>
+      <c r="E142" s="90" t="n"/>
+      <c r="F142" s="76" t="n"/>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="19" t="n"/>
       <c r="B143" s="20" t="n"/>
       <c r="C143" s="76" t="n"/>
       <c r="D143" s="68" t="n"/>
-      <c r="E143" s="76" t="n"/>
+      <c r="E143" s="90" t="n"/>
+      <c r="F143" s="76" t="n"/>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="19" t="n"/>
       <c r="B144" s="20" t="n"/>
       <c r="C144" s="76" t="n"/>
       <c r="D144" s="68" t="n"/>
-      <c r="E144" s="76" t="n"/>
+      <c r="E144" s="90" t="n"/>
+      <c r="F144" s="76" t="n"/>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="19" t="n"/>
       <c r="B145" s="20" t="n"/>
       <c r="C145" s="76" t="n"/>
       <c r="D145" s="68" t="n"/>
-      <c r="E145" s="76" t="n"/>
+      <c r="E145" s="90" t="n"/>
+      <c r="F145" s="76" t="n"/>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="19" t="n"/>
       <c r="B146" s="20" t="n"/>
       <c r="C146" s="76" t="n"/>
       <c r="D146" s="68" t="n"/>
-      <c r="E146" s="76" t="n"/>
+      <c r="E146" s="90" t="n"/>
+      <c r="F146" s="76" t="n"/>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="19" t="n"/>
       <c r="B147" s="20" t="n"/>
       <c r="C147" s="76" t="n"/>
       <c r="D147" s="68" t="n"/>
-      <c r="E147" s="76" t="n"/>
+      <c r="E147" s="90" t="n"/>
+      <c r="F147" s="76" t="n"/>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="19" t="n"/>
       <c r="B148" s="20" t="n"/>
       <c r="C148" s="76" t="n"/>
       <c r="D148" s="68" t="n"/>
-      <c r="E148" s="76" t="n"/>
+      <c r="E148" s="90" t="n"/>
+      <c r="F148" s="76" t="n"/>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="19" t="n"/>
       <c r="B149" s="20" t="n"/>
       <c r="C149" s="76" t="n"/>
       <c r="D149" s="68" t="n"/>
-      <c r="E149" s="76" t="n"/>
+      <c r="E149" s="90" t="n"/>
+      <c r="F149" s="76" t="n"/>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="19" t="n"/>
       <c r="B150" s="20" t="n"/>
       <c r="C150" s="76" t="n"/>
       <c r="D150" s="68" t="n"/>
-      <c r="E150" s="76" t="n"/>
+      <c r="E150" s="90" t="n"/>
+      <c r="F150" s="76" t="n"/>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="19" t="n"/>
       <c r="B151" s="20" t="n"/>
       <c r="C151" s="76" t="n"/>
       <c r="D151" s="68" t="n"/>
-      <c r="E151" s="76" t="n"/>
+      <c r="E151" s="90" t="n"/>
+      <c r="F151" s="76" t="n"/>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="19" t="n"/>
       <c r="B152" s="20" t="n"/>
       <c r="C152" s="76" t="n"/>
       <c r="D152" s="68" t="n"/>
-      <c r="E152" s="76" t="n"/>
+      <c r="E152" s="90" t="n"/>
+      <c r="F152" s="76" t="n"/>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="19" t="n"/>
       <c r="B153" s="20" t="n"/>
       <c r="C153" s="76" t="n"/>
       <c r="D153" s="68" t="n"/>
-      <c r="E153" s="76" t="n"/>
+      <c r="E153" s="90" t="n"/>
+      <c r="F153" s="76" t="n"/>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="19" t="n"/>
       <c r="B154" s="20" t="n"/>
       <c r="C154" s="76" t="n"/>
       <c r="D154" s="68" t="n"/>
-      <c r="E154" s="76" t="n"/>
+      <c r="E154" s="90" t="n"/>
+      <c r="F154" s="76" t="n"/>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="19" t="n"/>
       <c r="B155" s="20" t="n"/>
       <c r="C155" s="76" t="n"/>
       <c r="D155" s="68" t="n"/>
-      <c r="E155" s="76" t="n"/>
+      <c r="E155" s="90" t="n"/>
+      <c r="F155" s="76" t="n"/>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="19" t="n"/>
       <c r="B156" s="20" t="n"/>
       <c r="C156" s="76" t="n"/>
       <c r="D156" s="68" t="n"/>
-      <c r="E156" s="76" t="n"/>
+      <c r="E156" s="90" t="n"/>
+      <c r="F156" s="76" t="n"/>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="19" t="n"/>
       <c r="B157" s="20" t="n"/>
       <c r="C157" s="76" t="n"/>
       <c r="D157" s="68" t="n"/>
-      <c r="E157" s="76" t="n"/>
+      <c r="E157" s="90" t="n"/>
+      <c r="F157" s="76" t="n"/>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="19" t="n"/>
       <c r="B158" s="20" t="n"/>
       <c r="C158" s="76" t="n"/>
       <c r="D158" s="68" t="n"/>
-      <c r="E158" s="76" t="n"/>
+      <c r="E158" s="90" t="n"/>
+      <c r="F158" s="76" t="n"/>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="19" t="n"/>
       <c r="B159" s="20" t="n"/>
       <c r="C159" s="76" t="n"/>
       <c r="D159" s="68" t="n"/>
-      <c r="E159" s="76" t="n"/>
+      <c r="E159" s="90" t="n"/>
+      <c r="F159" s="76" t="n"/>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="19" t="n"/>
       <c r="B160" s="20" t="n"/>
       <c r="C160" s="76" t="n"/>
       <c r="D160" s="68" t="n"/>
-      <c r="E160" s="76" t="n"/>
+      <c r="E160" s="90" t="n"/>
+      <c r="F160" s="76" t="n"/>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="19" t="n"/>
       <c r="B161" s="20" t="n"/>
       <c r="C161" s="76" t="n"/>
       <c r="D161" s="68" t="n"/>
-      <c r="E161" s="76" t="n"/>
+      <c r="E161" s="90" t="n"/>
+      <c r="F161" s="76" t="n"/>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="19" t="n"/>
       <c r="B162" s="20" t="n"/>
       <c r="C162" s="76" t="n"/>
       <c r="D162" s="68" t="n"/>
-      <c r="E162" s="76" t="n"/>
+      <c r="E162" s="90" t="n"/>
+      <c r="F162" s="76" t="n"/>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="19" t="n"/>
       <c r="B163" s="20" t="n"/>
       <c r="C163" s="76" t="n"/>
       <c r="D163" s="68" t="n"/>
-      <c r="E163" s="76" t="n"/>
+      <c r="E163" s="90" t="n"/>
+      <c r="F163" s="76" t="n"/>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="19" t="n"/>
       <c r="B164" s="20" t="n"/>
       <c r="C164" s="76" t="n"/>
       <c r="D164" s="68" t="n"/>
-      <c r="E164" s="76" t="n"/>
+      <c r="E164" s="90" t="n"/>
+      <c r="F164" s="76" t="n"/>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="19" t="n"/>
       <c r="B165" s="20" t="n"/>
       <c r="C165" s="76" t="n"/>
       <c r="D165" s="68" t="n"/>
-      <c r="E165" s="76" t="n"/>
+      <c r="E165" s="90" t="n"/>
+      <c r="F165" s="76" t="n"/>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="19" t="n"/>
       <c r="B166" s="20" t="n"/>
       <c r="C166" s="76" t="n"/>
       <c r="D166" s="68" t="n"/>
-      <c r="E166" s="76" t="n"/>
+      <c r="E166" s="90" t="n"/>
+      <c r="F166" s="76" t="n"/>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="19" t="n"/>
       <c r="B167" s="20" t="n"/>
       <c r="C167" s="76" t="n"/>
       <c r="D167" s="68" t="n"/>
-      <c r="E167" s="76" t="n"/>
+      <c r="E167" s="90" t="n"/>
+      <c r="F167" s="76" t="n"/>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="19" t="n"/>
       <c r="B168" s="20" t="n"/>
       <c r="C168" s="76" t="n"/>
       <c r="D168" s="68" t="n"/>
-      <c r="E168" s="76" t="n"/>
+      <c r="E168" s="90" t="n"/>
+      <c r="F168" s="76" t="n"/>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="19" t="n"/>
       <c r="B169" s="20" t="n"/>
       <c r="C169" s="76" t="n"/>
       <c r="D169" s="68" t="n"/>
-      <c r="E169" s="76" t="n"/>
+      <c r="E169" s="90" t="n"/>
+      <c r="F169" s="76" t="n"/>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="19" t="n"/>
       <c r="B170" s="20" t="n"/>
       <c r="C170" s="76" t="n"/>
       <c r="D170" s="68" t="n"/>
-      <c r="E170" s="76" t="n"/>
+      <c r="E170" s="90" t="n"/>
+      <c r="F170" s="76" t="n"/>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="19" t="n"/>
       <c r="B171" s="20" t="n"/>
       <c r="C171" s="76" t="n"/>
       <c r="D171" s="68" t="n"/>
-      <c r="E171" s="76" t="n"/>
+      <c r="E171" s="90" t="n"/>
+      <c r="F171" s="76" t="n"/>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="19" t="n"/>
       <c r="B172" s="20" t="n"/>
       <c r="C172" s="76" t="n"/>
       <c r="D172" s="68" t="n"/>
-      <c r="E172" s="76" t="n"/>
+      <c r="E172" s="90" t="n"/>
+      <c r="F172" s="76" t="n"/>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="19" t="n"/>
       <c r="B173" s="20" t="n"/>
       <c r="C173" s="76" t="n"/>
       <c r="D173" s="68" t="n"/>
-      <c r="E173" s="76" t="n"/>
+      <c r="E173" s="90" t="n"/>
+      <c r="F173" s="76" t="n"/>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="19" t="n"/>
       <c r="B174" s="20" t="n"/>
       <c r="C174" s="76" t="n"/>
       <c r="D174" s="68" t="n"/>
-      <c r="E174" s="76" t="n"/>
+      <c r="E174" s="90" t="n"/>
+      <c r="F174" s="76" t="n"/>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="19" t="n"/>
       <c r="B175" s="20" t="n"/>
       <c r="C175" s="76" t="n"/>
       <c r="D175" s="68" t="n"/>
-      <c r="E175" s="76" t="n"/>
+      <c r="E175" s="90" t="n"/>
+      <c r="F175" s="76" t="n"/>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="19" t="n"/>
       <c r="B176" s="20" t="n"/>
       <c r="C176" s="76" t="n"/>
       <c r="D176" s="68" t="n"/>
-      <c r="E176" s="76" t="n"/>
+      <c r="E176" s="90" t="n"/>
+      <c r="F176" s="76" t="n"/>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="19" t="n"/>
       <c r="B177" s="20" t="n"/>
       <c r="C177" s="76" t="n"/>
       <c r="D177" s="68" t="n"/>
-      <c r="E177" s="76" t="n"/>
+      <c r="E177" s="90" t="n"/>
+      <c r="F177" s="76" t="n"/>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="19" t="n"/>
       <c r="B178" s="20" t="n"/>
       <c r="C178" s="76" t="n"/>
       <c r="D178" s="68" t="n"/>
-      <c r="E178" s="76" t="n"/>
+      <c r="E178" s="90" t="n"/>
+      <c r="F178" s="76" t="n"/>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="19" t="n"/>
       <c r="B179" s="20" t="n"/>
       <c r="C179" s="76" t="n"/>
       <c r="D179" s="68" t="n"/>
-      <c r="E179" s="76" t="n"/>
+      <c r="E179" s="90" t="n"/>
+      <c r="F179" s="76" t="n"/>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="19" t="n"/>
       <c r="B180" s="20" t="n"/>
       <c r="C180" s="76" t="n"/>
       <c r="D180" s="68" t="n"/>
-      <c r="E180" s="76" t="n"/>
+      <c r="E180" s="90" t="n"/>
+      <c r="F180" s="76" t="n"/>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="19" t="n"/>
       <c r="B181" s="20" t="n"/>
       <c r="C181" s="76" t="n"/>
       <c r="D181" s="68" t="n"/>
-      <c r="E181" s="76" t="n"/>
+      <c r="E181" s="90" t="n"/>
+      <c r="F181" s="76" t="n"/>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="19" t="n"/>
       <c r="B182" s="20" t="n"/>
       <c r="C182" s="76" t="n"/>
       <c r="D182" s="68" t="n"/>
-      <c r="E182" s="76" t="n"/>
+      <c r="E182" s="90" t="n"/>
+      <c r="F182" s="76" t="n"/>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="19" t="n"/>
       <c r="B183" s="20" t="n"/>
       <c r="C183" s="76" t="n"/>
       <c r="D183" s="68" t="n"/>
-      <c r="E183" s="76" t="n"/>
+      <c r="E183" s="90" t="n"/>
+      <c r="F183" s="76" t="n"/>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="19" t="n"/>
       <c r="B184" s="20" t="n"/>
       <c r="C184" s="76" t="n"/>
       <c r="D184" s="68" t="n"/>
-      <c r="E184" s="76" t="n"/>
+      <c r="E184" s="90" t="n"/>
+      <c r="F184" s="76" t="n"/>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="19" t="n"/>
       <c r="B185" s="20" t="n"/>
       <c r="C185" s="76" t="n"/>
       <c r="D185" s="68" t="n"/>
-      <c r="E185" s="76" t="n"/>
+      <c r="E185" s="90" t="n"/>
+      <c r="F185" s="76" t="n"/>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="19" t="n"/>
       <c r="B186" s="20" t="n"/>
       <c r="C186" s="76" t="n"/>
       <c r="D186" s="68" t="n"/>
-      <c r="E186" s="76" t="n"/>
+      <c r="E186" s="90" t="n"/>
+      <c r="F186" s="76" t="n"/>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="19" t="n"/>
       <c r="B187" s="20" t="n"/>
       <c r="C187" s="76" t="n"/>
       <c r="D187" s="68" t="n"/>
-      <c r="E187" s="76" t="n"/>
+      <c r="E187" s="90" t="n"/>
+      <c r="F187" s="76" t="n"/>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="19" t="n"/>
       <c r="B188" s="20" t="n"/>
       <c r="C188" s="76" t="n"/>
       <c r="D188" s="68" t="n"/>
-      <c r="E188" s="76" t="n"/>
+      <c r="E188" s="90" t="n"/>
+      <c r="F188" s="76" t="n"/>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="19" t="n"/>
       <c r="B189" s="20" t="n"/>
       <c r="C189" s="76" t="n"/>
       <c r="D189" s="68" t="n"/>
-      <c r="E189" s="76" t="n"/>
+      <c r="E189" s="90" t="n"/>
+      <c r="F189" s="76" t="n"/>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="19" t="n"/>
       <c r="B190" s="20" t="n"/>
       <c r="C190" s="76" t="n"/>
       <c r="D190" s="68" t="n"/>
-      <c r="E190" s="76" t="n"/>
+      <c r="E190" s="90" t="n"/>
+      <c r="F190" s="76" t="n"/>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="19" t="n"/>
       <c r="B191" s="20" t="n"/>
       <c r="C191" s="76" t="n"/>
       <c r="D191" s="68" t="n"/>
-      <c r="E191" s="76" t="n"/>
+      <c r="E191" s="90" t="n"/>
+      <c r="F191" s="76" t="n"/>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="19" t="n"/>
       <c r="B192" s="20" t="n"/>
       <c r="C192" s="76" t="n"/>
       <c r="D192" s="68" t="n"/>
-      <c r="E192" s="76" t="n"/>
+      <c r="E192" s="90" t="n"/>
+      <c r="F192" s="76" t="n"/>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="19" t="n"/>
       <c r="B193" s="20" t="n"/>
       <c r="C193" s="76" t="n"/>
       <c r="D193" s="68" t="n"/>
-      <c r="E193" s="76" t="n"/>
+      <c r="E193" s="90" t="n"/>
+      <c r="F193" s="76" t="n"/>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="19" t="n"/>
       <c r="B194" s="20" t="n"/>
       <c r="C194" s="76" t="n"/>
       <c r="D194" s="68" t="n"/>
-      <c r="E194" s="76" t="n"/>
+      <c r="E194" s="90" t="n"/>
+      <c r="F194" s="76" t="n"/>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="19" t="n"/>
       <c r="B195" s="20" t="n"/>
       <c r="C195" s="76" t="n"/>
       <c r="D195" s="68" t="n"/>
-      <c r="E195" s="76" t="n"/>
+      <c r="E195" s="90" t="n"/>
+      <c r="F195" s="76" t="n"/>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="19" t="n"/>
       <c r="B196" s="20" t="n"/>
       <c r="C196" s="76" t="n"/>
       <c r="D196" s="68" t="n"/>
-      <c r="E196" s="76" t="n"/>
+      <c r="E196" s="90" t="n"/>
+      <c r="F196" s="76" t="n"/>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="19" t="n"/>
       <c r="B197" s="20" t="n"/>
       <c r="C197" s="76" t="n"/>
       <c r="D197" s="68" t="n"/>
-      <c r="E197" s="76" t="n"/>
+      <c r="E197" s="90" t="n"/>
+      <c r="F197" s="76" t="n"/>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="19" t="n"/>
       <c r="B198" s="20" t="n"/>
       <c r="C198" s="76" t="n"/>
       <c r="D198" s="68" t="n"/>
-      <c r="E198" s="76" t="n"/>
+      <c r="E198" s="90" t="n"/>
+      <c r="F198" s="76" t="n"/>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="19" t="n"/>
       <c r="B199" s="20" t="n"/>
       <c r="C199" s="76" t="n"/>
       <c r="D199" s="68" t="n"/>
-      <c r="E199" s="76" t="n"/>
+      <c r="E199" s="90" t="n"/>
+      <c r="F199" s="76" t="n"/>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="19" t="n"/>
       <c r="B200" s="20" t="n"/>
       <c r="C200" s="76" t="n"/>
       <c r="D200" s="68" t="n"/>
-      <c r="E200" s="76" t="n"/>
+      <c r="E200" s="90" t="n"/>
+      <c r="F200" s="76" t="n"/>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="19" t="n"/>
       <c r="B201" s="20" t="n"/>
       <c r="C201" s="76" t="n"/>
       <c r="D201" s="68" t="n"/>
-      <c r="E201" s="76" t="n"/>
+      <c r="E201" s="90" t="n"/>
+      <c r="F201" s="76" t="n"/>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="19" t="n"/>
       <c r="B202" s="20" t="n"/>
       <c r="C202" s="76" t="n"/>
       <c r="D202" s="68" t="n"/>
-      <c r="E202" s="76" t="n"/>
+      <c r="E202" s="90" t="n"/>
+      <c r="F202" s="76" t="n"/>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="19" t="n"/>
       <c r="B203" s="20" t="n"/>
       <c r="C203" s="76" t="n"/>
       <c r="D203" s="68" t="n"/>
-      <c r="E203" s="76" t="n"/>
+      <c r="E203" s="90" t="n"/>
+      <c r="F203" s="76" t="n"/>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="19" t="n"/>
       <c r="B204" s="20" t="n"/>
       <c r="C204" s="76" t="n"/>
       <c r="D204" s="68" t="n"/>
-      <c r="E204" s="76" t="n"/>
+      <c r="E204" s="90" t="n"/>
+      <c r="F204" s="76" t="n"/>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="19" t="n"/>
       <c r="B205" s="20" t="n"/>
       <c r="C205" s="76" t="n"/>
       <c r="D205" s="68" t="n"/>
-      <c r="E205" s="76" t="n"/>
+      <c r="E205" s="90" t="n"/>
+      <c r="F205" s="76" t="n"/>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="19" t="n"/>
       <c r="B206" s="20" t="n"/>
       <c r="C206" s="76" t="n"/>
       <c r="D206" s="68" t="n"/>
-      <c r="E206" s="76" t="n"/>
+      <c r="E206" s="90" t="n"/>
+      <c r="F206" s="76" t="n"/>
     </row>
     <row r="207" ht="20" customHeight="1">
       <c r="A207" s="19" t="n"/>
       <c r="B207" s="20" t="n"/>
       <c r="C207" s="76" t="n"/>
       <c r="D207" s="68" t="n"/>
-      <c r="E207" s="76" t="n"/>
+      <c r="E207" s="90" t="n"/>
+      <c r="F207" s="76" t="n"/>
     </row>
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="19" t="n"/>
       <c r="B208" s="20" t="n"/>
       <c r="C208" s="76" t="n"/>
       <c r="D208" s="68" t="n"/>
-      <c r="E208" s="76" t="n"/>
+      <c r="E208" s="90" t="n"/>
+      <c r="F208" s="76" t="n"/>
     </row>
     <row r="209" ht="20" customHeight="1">
       <c r="A209" s="19" t="n"/>
       <c r="B209" s="20" t="n"/>
       <c r="C209" s="76" t="n"/>
       <c r="D209" s="68" t="n"/>
-      <c r="E209" s="76" t="n"/>
+      <c r="E209" s="90" t="n"/>
+      <c r="F209" s="76" t="n"/>
     </row>
     <row r="210" ht="20" customHeight="1">
       <c r="A210" s="19" t="n"/>
       <c r="B210" s="20" t="n"/>
       <c r="C210" s="76" t="n"/>
       <c r="D210" s="68" t="n"/>
-      <c r="E210" s="76" t="n"/>
+      <c r="E210" s="90" t="n"/>
+      <c r="F210" s="76" t="n"/>
     </row>
     <row r="211" ht="20" customHeight="1">
       <c r="A211" s="19" t="n"/>
       <c r="B211" s="20" t="n"/>
       <c r="C211" s="76" t="n"/>
       <c r="D211" s="68" t="n"/>
-      <c r="E211" s="76" t="n"/>
+      <c r="E211" s="90" t="n"/>
+      <c r="F211" s="76" t="n"/>
     </row>
     <row r="212" ht="20" customHeight="1">
       <c r="A212" s="19" t="n"/>
       <c r="B212" s="20" t="n"/>
       <c r="C212" s="76" t="n"/>
       <c r="D212" s="68" t="n"/>
-      <c r="E212" s="76" t="n"/>
+      <c r="E212" s="90" t="n"/>
+      <c r="F212" s="76" t="n"/>
     </row>
     <row r="213" ht="20" customHeight="1">
       <c r="A213" s="19" t="n"/>
       <c r="B213" s="20" t="n"/>
       <c r="C213" s="76" t="n"/>
       <c r="D213" s="68" t="n"/>
-      <c r="E213" s="76" t="n"/>
+      <c r="E213" s="90" t="n"/>
+      <c r="F213" s="76" t="n"/>
     </row>
     <row r="214" ht="20" customHeight="1">
       <c r="A214" s="19" t="n"/>
       <c r="B214" s="20" t="n"/>
       <c r="C214" s="76" t="n"/>
       <c r="D214" s="68" t="n"/>
-      <c r="E214" s="76" t="n"/>
+      <c r="E214" s="90" t="n"/>
+      <c r="F214" s="76" t="n"/>
     </row>
     <row r="215" ht="20" customHeight="1">
       <c r="A215" s="19" t="n"/>
       <c r="B215" s="20" t="n"/>
       <c r="C215" s="76" t="n"/>
       <c r="D215" s="68" t="n"/>
-      <c r="E215" s="76" t="n"/>
+      <c r="E215" s="90" t="n"/>
+      <c r="F215" s="76" t="n"/>
     </row>
     <row r="216" ht="20" customHeight="1">
       <c r="A216" s="19" t="n"/>
       <c r="B216" s="20" t="n"/>
       <c r="C216" s="76" t="n"/>
       <c r="D216" s="68" t="n"/>
-      <c r="E216" s="76" t="n"/>
+      <c r="E216" s="90" t="n"/>
+      <c r="F216" s="76" t="n"/>
     </row>
     <row r="217" ht="20" customHeight="1">
       <c r="A217" s="19" t="n"/>
       <c r="B217" s="20" t="n"/>
       <c r="C217" s="76" t="n"/>
       <c r="D217" s="68" t="n"/>
-      <c r="E217" s="76" t="n"/>
+      <c r="E217" s="90" t="n"/>
+      <c r="F217" s="76" t="n"/>
     </row>
     <row r="218" ht="20" customHeight="1">
       <c r="A218" s="19" t="n"/>
       <c r="B218" s="20" t="n"/>
       <c r="C218" s="76" t="n"/>
       <c r="D218" s="68" t="n"/>
-      <c r="E218" s="76" t="n"/>
+      <c r="E218" s="90" t="n"/>
+      <c r="F218" s="76" t="n"/>
     </row>
     <row r="219" ht="20" customHeight="1">
       <c r="A219" s="19" t="n"/>
       <c r="B219" s="20" t="n"/>
       <c r="C219" s="76" t="n"/>
       <c r="D219" s="68" t="n"/>
-      <c r="E219" s="76" t="n"/>
+      <c r="E219" s="90" t="n"/>
+      <c r="F219" s="76" t="n"/>
     </row>
     <row r="220" ht="20" customHeight="1">
       <c r="A220" s="19" t="n"/>
       <c r="B220" s="20" t="n"/>
       <c r="C220" s="76" t="n"/>
       <c r="D220" s="68" t="n"/>
-      <c r="E220" s="76" t="n"/>
+      <c r="E220" s="90" t="n"/>
+      <c r="F220" s="76" t="n"/>
     </row>
     <row r="221" ht="20" customHeight="1">
       <c r="A221" s="19" t="n"/>
       <c r="B221" s="20" t="n"/>
       <c r="C221" s="76" t="n"/>
       <c r="D221" s="68" t="n"/>
-      <c r="E221" s="76" t="n"/>
+      <c r="E221" s="90" t="n"/>
+      <c r="F221" s="76" t="n"/>
     </row>
     <row r="222" ht="20" customHeight="1">
       <c r="A222" s="19" t="n"/>
       <c r="B222" s="20" t="n"/>
       <c r="C222" s="76" t="n"/>
       <c r="D222" s="68" t="n"/>
-      <c r="E222" s="76" t="n"/>
+      <c r="E222" s="90" t="n"/>
+      <c r="F222" s="76" t="n"/>
     </row>
     <row r="223" ht="20" customHeight="1">
       <c r="A223" s="19" t="n"/>
       <c r="B223" s="20" t="n"/>
       <c r="C223" s="76" t="n"/>
       <c r="D223" s="68" t="n"/>
-      <c r="E223" s="76" t="n"/>
+      <c r="E223" s="90" t="n"/>
+      <c r="F223" s="76" t="n"/>
     </row>
     <row r="224" ht="20" customHeight="1">
       <c r="A224" s="19" t="n"/>
       <c r="B224" s="20" t="n"/>
       <c r="C224" s="76" t="n"/>
       <c r="D224" s="68" t="n"/>
-      <c r="E224" s="76" t="n"/>
+      <c r="E224" s="90" t="n"/>
+      <c r="F224" s="76" t="n"/>
     </row>
     <row r="225" ht="20" customHeight="1">
       <c r="A225" s="19" t="n"/>
       <c r="B225" s="20" t="n"/>
       <c r="C225" s="76" t="n"/>
       <c r="D225" s="68" t="n"/>
-      <c r="E225" s="76" t="n"/>
+      <c r="E225" s="90" t="n"/>
+      <c r="F225" s="76" t="n"/>
     </row>
     <row r="226" ht="20" customHeight="1">
       <c r="A226" s="19" t="n"/>
       <c r="B226" s="20" t="n"/>
       <c r="C226" s="76" t="n"/>
       <c r="D226" s="68" t="n"/>
-      <c r="E226" s="76" t="n"/>
+      <c r="E226" s="90" t="n"/>
+      <c r="F226" s="76" t="n"/>
     </row>
     <row r="227" ht="20" customHeight="1">
       <c r="A227" s="19" t="n"/>
       <c r="B227" s="20" t="n"/>
       <c r="C227" s="76" t="n"/>
       <c r="D227" s="68" t="n"/>
-      <c r="E227" s="76" t="n"/>
+      <c r="E227" s="90" t="n"/>
+      <c r="F227" s="76" t="n"/>
     </row>
     <row r="228" ht="20" customHeight="1">
       <c r="A228" s="19" t="n"/>
       <c r="B228" s="20" t="n"/>
       <c r="C228" s="76" t="n"/>
       <c r="D228" s="68" t="n"/>
-      <c r="E228" s="76" t="n"/>
+      <c r="E228" s="90" t="n"/>
+      <c r="F228" s="76" t="n"/>
     </row>
     <row r="229" ht="20" customHeight="1">
       <c r="A229" s="19" t="n"/>
       <c r="B229" s="20" t="n"/>
       <c r="C229" s="76" t="n"/>
       <c r="D229" s="68" t="n"/>
-      <c r="E229" s="76" t="n"/>
+      <c r="E229" s="90" t="n"/>
+      <c r="F229" s="76" t="n"/>
     </row>
     <row r="230" ht="20" customHeight="1">
       <c r="A230" s="19" t="n"/>
       <c r="B230" s="20" t="n"/>
       <c r="C230" s="76" t="n"/>
       <c r="D230" s="68" t="n"/>
-      <c r="E230" s="76" t="n"/>
+      <c r="E230" s="90" t="n"/>
+      <c r="F230" s="76" t="n"/>
     </row>
     <row r="231" ht="20" customHeight="1">
       <c r="A231" s="19" t="n"/>
       <c r="B231" s="20" t="n"/>
       <c r="C231" s="76" t="n"/>
       <c r="D231" s="68" t="n"/>
-      <c r="E231" s="76" t="n"/>
+      <c r="E231" s="90" t="n"/>
+      <c r="F231" s="76" t="n"/>
     </row>
     <row r="232" ht="20" customHeight="1">
       <c r="A232" s="19" t="n"/>
       <c r="B232" s="20" t="n"/>
       <c r="C232" s="76" t="n"/>
       <c r="D232" s="68" t="n"/>
-      <c r="E232" s="76" t="n"/>
+      <c r="E232" s="90" t="n"/>
+      <c r="F232" s="76" t="n"/>
     </row>
     <row r="233" ht="20" customHeight="1">
       <c r="A233" s="19" t="n"/>
       <c r="B233" s="20" t="n"/>
       <c r="C233" s="76" t="n"/>
       <c r="D233" s="68" t="n"/>
-      <c r="E233" s="76" t="n"/>
+      <c r="E233" s="90" t="n"/>
+      <c r="F233" s="76" t="n"/>
     </row>
     <row r="234" ht="20" customHeight="1">
       <c r="A234" s="19" t="n"/>
       <c r="B234" s="20" t="n"/>
       <c r="C234" s="76" t="n"/>
       <c r="D234" s="68" t="n"/>
-      <c r="E234" s="76" t="n"/>
+      <c r="E234" s="90" t="n"/>
+      <c r="F234" s="76" t="n"/>
     </row>
     <row r="235" ht="20" customHeight="1">
       <c r="A235" s="19" t="n"/>
       <c r="B235" s="20" t="n"/>
       <c r="C235" s="76" t="n"/>
       <c r="D235" s="68" t="n"/>
-      <c r="E235" s="76" t="n"/>
+      <c r="E235" s="90" t="n"/>
+      <c r="F235" s="76" t="n"/>
     </row>
     <row r="236" ht="20" customHeight="1">
       <c r="A236" s="19" t="n"/>
       <c r="B236" s="20" t="n"/>
       <c r="C236" s="76" t="n"/>
       <c r="D236" s="68" t="n"/>
-      <c r="E236" s="76" t="n"/>
+      <c r="E236" s="90" t="n"/>
+      <c r="F236" s="76" t="n"/>
     </row>
     <row r="237" ht="20" customHeight="1">
       <c r="A237" s="19" t="n"/>
       <c r="B237" s="20" t="n"/>
       <c r="C237" s="76" t="n"/>
       <c r="D237" s="68" t="n"/>
-      <c r="E237" s="76" t="n"/>
+      <c r="E237" s="90" t="n"/>
+      <c r="F237" s="76" t="n"/>
     </row>
     <row r="238" ht="20" customHeight="1">
       <c r="A238" s="19" t="n"/>
       <c r="B238" s="20" t="n"/>
       <c r="C238" s="76" t="n"/>
       <c r="D238" s="68" t="n"/>
-      <c r="E238" s="76" t="n"/>
+      <c r="E238" s="90" t="n"/>
+      <c r="F238" s="76" t="n"/>
     </row>
     <row r="239" ht="20" customHeight="1">
       <c r="A239" s="19" t="n"/>
       <c r="B239" s="20" t="n"/>
       <c r="C239" s="76" t="n"/>
       <c r="D239" s="68" t="n"/>
-      <c r="E239" s="76" t="n"/>
+      <c r="E239" s="90" t="n"/>
+      <c r="F239" s="76" t="n"/>
     </row>
     <row r="240" ht="20" customHeight="1">
       <c r="A240" s="19" t="n"/>
       <c r="B240" s="20" t="n"/>
       <c r="C240" s="76" t="n"/>
       <c r="D240" s="68" t="n"/>
-      <c r="E240" s="76" t="n"/>
+      <c r="E240" s="90" t="n"/>
+      <c r="F240" s="76" t="n"/>
     </row>
     <row r="241" ht="20" customHeight="1">
       <c r="A241" s="19" t="n"/>
       <c r="B241" s="20" t="n"/>
       <c r="C241" s="76" t="n"/>
       <c r="D241" s="68" t="n"/>
-      <c r="E241" s="76" t="n"/>
+      <c r="E241" s="90" t="n"/>
+      <c r="F241" s="76" t="n"/>
     </row>
     <row r="242" ht="20" customHeight="1">
       <c r="A242" s="19" t="n"/>
       <c r="B242" s="20" t="n"/>
       <c r="C242" s="76" t="n"/>
       <c r="D242" s="68" t="n"/>
-      <c r="E242" s="76" t="n"/>
+      <c r="E242" s="90" t="n"/>
+      <c r="F242" s="76" t="n"/>
     </row>
     <row r="243" ht="20" customHeight="1">
       <c r="A243" s="19" t="n"/>
       <c r="B243" s="20" t="n"/>
       <c r="C243" s="76" t="n"/>
       <c r="D243" s="68" t="n"/>
-      <c r="E243" s="76" t="n"/>
+      <c r="E243" s="90" t="n"/>
+      <c r="F243" s="76" t="n"/>
     </row>
     <row r="244" ht="20" customHeight="1">
       <c r="A244" s="19" t="n"/>
       <c r="B244" s="20" t="n"/>
       <c r="C244" s="76" t="n"/>
       <c r="D244" s="68" t="n"/>
-      <c r="E244" s="76" t="n"/>
+      <c r="E244" s="90" t="n"/>
+      <c r="F244" s="76" t="n"/>
     </row>
     <row r="245" ht="20" customHeight="1">
       <c r="A245" s="19" t="n"/>
       <c r="B245" s="20" t="n"/>
       <c r="C245" s="76" t="n"/>
       <c r="D245" s="68" t="n"/>
-      <c r="E245" s="76" t="n"/>
+      <c r="E245" s="90" t="n"/>
+      <c r="F245" s="76" t="n"/>
     </row>
     <row r="246" ht="20" customHeight="1">
       <c r="A246" s="19" t="n"/>
       <c r="B246" s="20" t="n"/>
       <c r="C246" s="76" t="n"/>
       <c r="D246" s="68" t="n"/>
-      <c r="E246" s="76" t="n"/>
+      <c r="E246" s="90" t="n"/>
+      <c r="F246" s="76" t="n"/>
     </row>
     <row r="247" ht="20" customHeight="1">
       <c r="A247" s="19" t="n"/>
       <c r="B247" s="20" t="n"/>
       <c r="C247" s="76" t="n"/>
       <c r="D247" s="68" t="n"/>
-      <c r="E247" s="76" t="n"/>
+      <c r="E247" s="90" t="n"/>
+      <c r="F247" s="76" t="n"/>
     </row>
     <row r="248" ht="20" customHeight="1">
       <c r="A248" s="19" t="n"/>
       <c r="B248" s="20" t="n"/>
       <c r="C248" s="76" t="n"/>
       <c r="D248" s="68" t="n"/>
-      <c r="E248" s="76" t="n"/>
+      <c r="E248" s="90" t="n"/>
+      <c r="F248" s="76" t="n"/>
     </row>
     <row r="249" ht="20" customHeight="1">
       <c r="A249" s="19" t="n"/>
       <c r="B249" s="20" t="n"/>
       <c r="C249" s="76" t="n"/>
       <c r="D249" s="68" t="n"/>
-      <c r="E249" s="76" t="n"/>
+      <c r="E249" s="90" t="n"/>
+      <c r="F249" s="76" t="n"/>
     </row>
     <row r="250" ht="20" customHeight="1">
       <c r="A250" s="19" t="n"/>
       <c r="B250" s="20" t="n"/>
       <c r="C250" s="76" t="n"/>
       <c r="D250" s="68" t="n"/>
-      <c r="E250" s="76" t="n"/>
+      <c r="E250" s="90" t="n"/>
+      <c r="F250" s="76" t="n"/>
     </row>
     <row r="251" ht="20" customHeight="1">
       <c r="A251" s="19" t="n"/>
       <c r="B251" s="20" t="n"/>
       <c r="C251" s="76" t="n"/>
       <c r="D251" s="68" t="n"/>
-      <c r="E251" s="76" t="n"/>
+      <c r="E251" s="90" t="n"/>
+      <c r="F251" s="76" t="n"/>
     </row>
     <row r="252" ht="20" customHeight="1">
       <c r="A252" s="19" t="n"/>
       <c r="B252" s="20" t="n"/>
       <c r="C252" s="76" t="n"/>
       <c r="D252" s="68" t="n"/>
-      <c r="E252" s="76" t="n"/>
+      <c r="E252" s="90" t="n"/>
+      <c r="F252" s="76" t="n"/>
     </row>
     <row r="254" ht="28" customHeight="1">
       <c r="A254" s="24" t="inlineStr">
         <is>
-          <t>זו רשימת ההיצע לגיליון «שיבוץ». מותר ורצוי להוסיף, למחוק ולתקן — הרשימה הנגללת והקטגוריה האוטומטית מתעדכנות לבד. משימות ניקיון מופיעות בנפרד לכל מרחב, כדי לבחור בכל שבת אילו מרחבים מנקים ומתי. עמודת «עוגן» היא ברירת המחדל לשיוך המשימה בלו"ז הצל.</t>
+          <t>זו רשימת ההיצע לגיליון «שיבוץ». מותר ורצוי להוסיף, למחוק ולתקן — הרשימה הנגללת והקטגוריה האוטומטית מתעדכנות לבד. משימות ניקיון מופיעות בנפרד לכל מרחב, כדי לבחור בכל שבת אילו מרחבים מנקים ומתי. «שעה» ו«עוגן» הן ברירות המחדל שנכתבות לשיבוץ ומשם ללו"ז הצל.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A254:D254"/>
+    <mergeCell ref="A254:F254"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="A3:A252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -17936,7 +18123,7 @@
     <dataValidation sqref="C3:C252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"שישי,שבת,מוצאי שבת,חמישי,משתנה"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"חמישי — הכנות,שישי — ארוחת בוקר,שישי — הכנות ועבודה,שישי — ארוחת צהריים,קבלת שבת ישראלית,כניסת שבת,קבלת שבת וערבית,סעודת שבת,טיש עם איש צוות,קידוש,חבורות חניכים,ארוחת צהריים,חבורה עם איש צוות,סעודה שלישית,הבדלה,ניקיונות וארגון הקמפוס,כריכה לכריכה"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23534,7 +23721,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>לוח שבתות — זמני ירושלים</t>
         </is>
@@ -23568,7 +23755,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="n">
+      <c r="A3" s="95" t="n">
         <v>46269</v>
       </c>
       <c r="B3" s="20" t="inlineStr">
@@ -23582,14 +23769,14 @@
       <c r="D3" s="82" t="n">
         <v>0.81875</v>
       </c>
-      <c r="E3" s="95" t="inlineStr">
+      <c r="E3" s="96" t="inlineStr">
         <is>
           <t>הזמנים מחושבים לירושלים (כניסה 40 דק' לפני השקיעה, צאה 40 דק' אחריה) ומדויקים לדקה-שתיים. אם הלוח שלך אומר אחרת — תקנו את השורה. הצבע הצהוב מסמן שדה שמותר לשנות.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="n">
+      <c r="A4" s="95" t="n">
         <v>46276</v>
       </c>
       <c r="B4" s="20" t="inlineStr">
@@ -23605,7 +23792,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="n">
+      <c r="A5" s="95" t="n">
         <v>46283</v>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -23621,7 +23808,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="n">
+      <c r="A6" s="95" t="n">
         <v>46290</v>
       </c>
       <c r="B6" s="20" t="inlineStr">
@@ -23637,7 +23824,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="94" t="n">
+      <c r="A7" s="95" t="n">
         <v>46297</v>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -23653,7 +23840,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="94" t="n">
+      <c r="A8" s="95" t="n">
         <v>46304</v>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -23669,7 +23856,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="94" t="n">
+      <c r="A9" s="95" t="n">
         <v>46311</v>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -23685,7 +23872,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="n">
+      <c r="A10" s="95" t="n">
         <v>46318</v>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -23701,7 +23888,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="94" t="n">
+      <c r="A11" s="95" t="n">
         <v>46325</v>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -23717,7 +23904,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="n">
+      <c r="A12" s="95" t="n">
         <v>46332</v>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -23733,7 +23920,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="n">
+      <c r="A13" s="95" t="n">
         <v>46339</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -23749,7 +23936,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="n">
+      <c r="A14" s="95" t="n">
         <v>46346</v>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -23765,7 +23952,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="94" t="n">
+      <c r="A15" s="95" t="n">
         <v>46353</v>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -23781,7 +23968,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="94" t="n">
+      <c r="A16" s="95" t="n">
         <v>46360</v>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -23797,7 +23984,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="94" t="n">
+      <c r="A17" s="95" t="n">
         <v>46367</v>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -23813,7 +24000,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="94" t="n">
+      <c r="A18" s="95" t="n">
         <v>46374</v>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -23829,7 +24016,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="94" t="n">
+      <c r="A19" s="95" t="n">
         <v>46381</v>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -23845,7 +24032,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="94" t="n">
+      <c r="A20" s="95" t="n">
         <v>46388</v>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -23861,7 +24048,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="n">
+      <c r="A21" s="95" t="n">
         <v>46395</v>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -23877,7 +24064,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="94" t="n">
+      <c r="A22" s="95" t="n">
         <v>46402</v>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -23893,7 +24080,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="94" t="n">
+      <c r="A23" s="95" t="n">
         <v>46409</v>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -23909,7 +24096,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="94" t="n">
+      <c r="A24" s="95" t="n">
         <v>46416</v>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -23925,7 +24112,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="n">
+      <c r="A25" s="95" t="n">
         <v>46423</v>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -23941,7 +24128,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="94" t="n">
+      <c r="A26" s="95" t="n">
         <v>46430</v>
       </c>
       <c r="B26" s="20" t="inlineStr">
@@ -23957,7 +24144,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="94" t="n">
+      <c r="A27" s="95" t="n">
         <v>46437</v>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -23973,7 +24160,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="94" t="n">
+      <c r="A28" s="95" t="n">
         <v>46444</v>
       </c>
       <c r="B28" s="20" t="inlineStr">
@@ -23989,7 +24176,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="94" t="n">
+      <c r="A29" s="95" t="n">
         <v>46451</v>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -24005,7 +24192,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="94" t="n">
+      <c r="A30" s="95" t="n">
         <v>46458</v>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -24021,7 +24208,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="94" t="n">
+      <c r="A31" s="95" t="n">
         <v>46465</v>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -24037,7 +24224,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="94" t="n">
+      <c r="A32" s="95" t="n">
         <v>46472</v>
       </c>
       <c r="B32" s="20" t="inlineStr">
@@ -24053,7 +24240,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="94" t="n">
+      <c r="A33" s="95" t="n">
         <v>46479</v>
       </c>
       <c r="B33" s="20" t="inlineStr">
@@ -24069,7 +24256,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="n">
+      <c r="A34" s="95" t="n">
         <v>46486</v>
       </c>
       <c r="B34" s="20" t="inlineStr">
@@ -24085,7 +24272,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="94" t="n">
+      <c r="A35" s="95" t="n">
         <v>46493</v>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -24101,7 +24288,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="94" t="n">
+      <c r="A36" s="95" t="n">
         <v>46500</v>
       </c>
       <c r="B36" s="20" t="inlineStr">
@@ -24117,7 +24304,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="94" t="n">
+      <c r="A37" s="95" t="n">
         <v>46507</v>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -24133,7 +24320,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="94" t="n">
+      <c r="A38" s="95" t="n">
         <v>46514</v>
       </c>
       <c r="B38" s="20" t="inlineStr">
@@ -24149,7 +24336,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="94" t="n">
+      <c r="A39" s="95" t="n">
         <v>46521</v>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -24165,7 +24352,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="94" t="n">
+      <c r="A40" s="95" t="n">
         <v>46528</v>
       </c>
       <c r="B40" s="20" t="inlineStr">
@@ -24181,7 +24368,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="94" t="n">
+      <c r="A41" s="95" t="n">
         <v>46535</v>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -24197,7 +24384,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="94" t="n">
+      <c r="A42" s="95" t="n">
         <v>46542</v>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -24213,7 +24400,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="94" t="n">
+      <c r="A43" s="95" t="n">
         <v>46549</v>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -24229,7 +24416,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="94" t="n">
+      <c r="A44" s="95" t="n">
         <v>46556</v>
       </c>
       <c r="B44" s="20" t="inlineStr">
@@ -24245,7 +24432,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="94" t="n">
+      <c r="A45" s="95" t="n">
         <v>46563</v>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -24261,7 +24448,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="94" t="n">
+      <c r="A46" s="95" t="n">
         <v>46570</v>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -24277,7 +24464,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="94" t="n">
+      <c r="A47" s="95" t="n">
         <v>46577</v>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -24293,7 +24480,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="94" t="n">
+      <c r="A48" s="95" t="n">
         <v>46584</v>
       </c>
       <c r="B48" s="20" t="inlineStr">
@@ -24309,7 +24496,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="94" t="n">
+      <c r="A49" s="95" t="n">
         <v>46591</v>
       </c>
       <c r="B49" s="20" t="inlineStr">
@@ -24325,7 +24512,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="94" t="n">
+      <c r="A50" s="95" t="n">
         <v>46598</v>
       </c>
       <c r="B50" s="20" t="inlineStr">
@@ -24341,7 +24528,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="94" t="n">
+      <c r="A51" s="95" t="n">
         <v>46605</v>
       </c>
       <c r="B51" s="20" t="inlineStr">
@@ -24357,7 +24544,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="94" t="n">
+      <c r="A52" s="95" t="n">
         <v>46612</v>
       </c>
       <c r="B52" s="20" t="inlineStr">
@@ -24373,7 +24560,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="94" t="n">
+      <c r="A53" s="95" t="n">
         <v>46619</v>
       </c>
       <c r="B53" s="20" t="inlineStr">
@@ -24389,7 +24576,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="94" t="n">
+      <c r="A54" s="95" t="n">
         <v>46626</v>
       </c>
       <c r="B54" s="20" t="inlineStr">
